--- a/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Evolution_Library.xlsx
+++ b/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Evolution_Library.xlsx
@@ -11,13 +11,15 @@
     <sheet name="Kombinationer" sheetId="4" r:id="rId4"/>
     <sheet name="Favoriter" sheetId="5" r:id="rId5"/>
     <sheet name="Designregler" sheetId="6" r:id="rId6"/>
+    <sheet name="Unified Index" sheetId="7" r:id="rIdUnified1"/>
+    <sheet name="JAC Ideas" sheetId="8" r:id="rIdUnified2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Aptos"/>
@@ -34,8 +36,31 @@
       <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -54,8 +79,19 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF334155"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -63,11 +99,13 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -78,8 +116,55 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
 </styleSheet>
+</file>
+
+<file path=xl/tables/unified1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="101" name="UnifiedIdeas" displayName="UnifiedIdeas" ref="A1:H183" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <tableColumns count="8">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Name"/>
+    <tableColumn id="3" name="Kind"/>
+    <tableColumn id="4" name="Base / Participants"/>
+    <tableColumn id="5" name="Tags"/>
+    <tableColumn id="6" name="Origin"/>
+    <tableColumn id="7" name="Status"/>
+    <tableColumn id="8" name="Canonical detail"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/unified2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="102" name="JacIdeas" displayName="JacIdeas" ref="A1:H69" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <tableColumns count="8">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Name"/>
+    <tableColumn id="3" name="Base / Participants"/>
+    <tableColumn id="4" name="Idea (draft; historical values are not balance)"/>
+    <tableColumn id="5" name="Origin"/>
+    <tableColumn id="6" name="Status"/>
+    <tableColumn id="7" name="Provenance"/>
+    <tableColumn id="8" name="Canonical detail"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9535,4 +9620,6540 @@
   <autoFilter ref="A4:E33"/>
   <pageMargins left=".3" right=".3" top=".5" bottom=".5" header=".2" footer=".2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="40" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="40" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="40" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="40" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="40" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="40" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="10" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" s="10" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C1" s="10" t="str">
+        <v>Kind</v>
+      </c>
+      <c r="D1" s="10" t="str">
+        <v>Base / Participants</v>
+      </c>
+      <c r="E1" s="10" t="str">
+        <v>Tags</v>
+      </c>
+      <c r="F1" s="10" t="str">
+        <v>Origin</v>
+      </c>
+      <c r="G1" s="10" t="str">
+        <v>Status</v>
+      </c>
+      <c r="H1" s="10" t="str">
+        <v>Canonical detail</v>
+      </c>
+    </row>
+    <row r="2" ht="80" customHeight="1">
+      <c r="A2" s="7" t="str">
+        <v>GEN-01</v>
+      </c>
+      <c r="B2" s="7" t="str">
+        <v>Pulse Mend</v>
+      </c>
+      <c r="C2" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D2" s="7" t="str"/>
+      <c r="E2" s="7" t="str">
+        <v>healing</v>
+      </c>
+      <c r="F2" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G2" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H2" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#gen-01</v>
+      </c>
+    </row>
+    <row r="3" ht="80" customHeight="1">
+      <c r="A3" s="7" t="str">
+        <v>GEN-01-E01</v>
+      </c>
+      <c r="B3" s="7" t="str">
+        <v>Vital Crescendo</v>
+      </c>
+      <c r="C3" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D3" s="7" t="str">
+        <v>GEN-01</v>
+      </c>
+      <c r="E3" s="7" t="str">
+        <v>healing, timing</v>
+      </c>
+      <c r="F3" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G3" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H3" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#gen-01-e01</v>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" s="7" t="str">
+        <v>GEN-01-E02</v>
+      </c>
+      <c r="B4" s="7" t="str">
+        <v>Second Heart</v>
+      </c>
+      <c r="C4" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D4" s="7" t="str">
+        <v>GEN-01</v>
+      </c>
+      <c r="E4" s="7" t="str">
+        <v>healing</v>
+      </c>
+      <c r="F4" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G4" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H4" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#gen-01-e02</v>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1">
+      <c r="A5" s="7" t="str">
+        <v>GEN-01-E03</v>
+      </c>
+      <c r="B5" s="7" t="str">
+        <v>Vital Reversal</v>
+      </c>
+      <c r="C5" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D5" s="7" t="str">
+        <v>GEN-01</v>
+      </c>
+      <c r="E5" s="7" t="str">
+        <v>healing, protection</v>
+      </c>
+      <c r="F5" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G5" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H5" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#gen-01-e03</v>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="7" t="str">
+        <v>GEN-02</v>
+      </c>
+      <c r="B6" s="7" t="str">
+        <v>Resonance Guard</v>
+      </c>
+      <c r="C6" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D6" s="7" t="str"/>
+      <c r="E6" s="7" t="str">
+        <v>protection</v>
+      </c>
+      <c r="F6" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G6" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H6" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#gen-02</v>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="7" t="str">
+        <v>GEN-02-E01</v>
+      </c>
+      <c r="B7" s="7" t="str">
+        <v>Guardian Network</v>
+      </c>
+      <c r="C7" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D7" s="7" t="str">
+        <v>GEN-02</v>
+      </c>
+      <c r="E7" s="7" t="str">
+        <v>protection</v>
+      </c>
+      <c r="F7" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G7" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H7" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#gen-02-e01</v>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="7" t="str">
+        <v>GEN-02-E02</v>
+      </c>
+      <c r="B8" s="7" t="str">
+        <v>Retaliation</v>
+      </c>
+      <c r="C8" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D8" s="7" t="str">
+        <v>GEN-02</v>
+      </c>
+      <c r="E8" s="7" t="str">
+        <v>protection, area</v>
+      </c>
+      <c r="F8" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G8" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H8" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#gen-02-e02</v>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="7" t="str">
+        <v>GEN-02-E03</v>
+      </c>
+      <c r="B9" s="7" t="str">
+        <v>Last Stand</v>
+      </c>
+      <c r="C9" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D9" s="7" t="str">
+        <v>GEN-02</v>
+      </c>
+      <c r="E9" s="7" t="str">
+        <v>healing, protection</v>
+      </c>
+      <c r="F9" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G9" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H9" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#gen-02-e03</v>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="7" t="str">
+        <v>GEN-03</v>
+      </c>
+      <c r="B10" s="7" t="str">
+        <v>Vital Cascade</v>
+      </c>
+      <c r="C10" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D10" s="7" t="str"/>
+      <c r="E10" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F10" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G10" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H10" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#gen-03</v>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="7" t="str">
+        <v>GEN-03-E01</v>
+      </c>
+      <c r="B11" s="7" t="str">
+        <v>Double Cascade</v>
+      </c>
+      <c r="C11" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D11" s="7" t="str">
+        <v>GEN-03</v>
+      </c>
+      <c r="E11" s="7" t="str">
+        <v>healing</v>
+      </c>
+      <c r="F11" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G11" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H11" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#gen-03-e01</v>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
+      <c r="A12" s="7" t="str">
+        <v>GEN-03-E02</v>
+      </c>
+      <c r="B12" s="7" t="str">
+        <v>Rejuvenating Orbit</v>
+      </c>
+      <c r="C12" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D12" s="7" t="str">
+        <v>GEN-03</v>
+      </c>
+      <c r="E12" s="7" t="str">
+        <v>healing</v>
+      </c>
+      <c r="F12" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G12" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H12" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#gen-03-e02</v>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="7" t="str">
+        <v>GEN-03-E03</v>
+      </c>
+      <c r="B13" s="7" t="str">
+        <v>Life Transfer</v>
+      </c>
+      <c r="C13" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D13" s="7" t="str">
+        <v>GEN-03</v>
+      </c>
+      <c r="E13" s="7" t="str">
+        <v>healing</v>
+      </c>
+      <c r="F13" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G13" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H13" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#gen-03-e03</v>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
+      <c r="A14" s="7" t="str">
+        <v>GEN-04</v>
+      </c>
+      <c r="B14" s="7" t="str">
+        <v>Stasis Seal</v>
+      </c>
+      <c r="C14" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D14" s="7" t="str"/>
+      <c r="E14" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F14" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G14" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H14" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#gen-04</v>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1">
+      <c r="A15" s="7" t="str">
+        <v>GEN-04-E01</v>
+      </c>
+      <c r="B15" s="7" t="str">
+        <v>Tranquility Wave</v>
+      </c>
+      <c r="C15" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D15" s="7" t="str">
+        <v>GEN-04</v>
+      </c>
+      <c r="E15" s="7" t="str">
+        <v>control, area</v>
+      </c>
+      <c r="F15" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G15" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H15" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#gen-04-e01</v>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="7" t="str">
+        <v>GEN-04-E02</v>
+      </c>
+      <c r="B16" s="7" t="str">
+        <v>Mercy Bloom</v>
+      </c>
+      <c r="C16" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D16" s="7" t="str">
+        <v>GEN-04</v>
+      </c>
+      <c r="E16" s="7" t="str">
+        <v>healing</v>
+      </c>
+      <c r="F16" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G16" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H16" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#gen-04-e02</v>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1">
+      <c r="A17" s="7" t="str">
+        <v>GEN-04-E03</v>
+      </c>
+      <c r="B17" s="7" t="str">
+        <v>Essence Siphon</v>
+      </c>
+      <c r="C17" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D17" s="7" t="str">
+        <v>GEN-04</v>
+      </c>
+      <c r="E17" s="7" t="str">
+        <v>healing</v>
+      </c>
+      <c r="F17" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G17" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H17" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#gen-04-e03</v>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1">
+      <c r="A18" s="7" t="str">
+        <v>GEN-05</v>
+      </c>
+      <c r="B18" s="7" t="str">
+        <v>Vital Recall</v>
+      </c>
+      <c r="C18" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D18" s="7" t="str"/>
+      <c r="E18" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F18" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G18" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H18" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#gen-05</v>
+      </c>
+    </row>
+    <row r="19" ht="80" customHeight="1">
+      <c r="A19" s="7" t="str">
+        <v>GEN-06</v>
+      </c>
+      <c r="B19" s="7" t="str">
+        <v>Soul Relay</v>
+      </c>
+      <c r="C19" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D19" s="7" t="str"/>
+      <c r="E19" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F19" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G19" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H19" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#gen-06</v>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1">
+      <c r="A20" s="7" t="str">
+        <v>IMP-01</v>
+      </c>
+      <c r="B20" s="7" t="str">
+        <v>Phase Rush</v>
+      </c>
+      <c r="C20" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D20" s="7" t="str"/>
+      <c r="E20" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F20" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G20" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H20" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#imp-01</v>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" s="7" t="str">
+        <v>IMP-01-E01</v>
+      </c>
+      <c r="B21" s="7" t="str">
+        <v>Meteor Charge</v>
+      </c>
+      <c r="C21" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D21" s="7" t="str">
+        <v>IMP-01</v>
+      </c>
+      <c r="E21" s="7" t="str">
+        <v>movement, area</v>
+      </c>
+      <c r="F21" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G21" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H21" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#imp-01-e01</v>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" s="7" t="str">
+        <v>IMP-01-E02</v>
+      </c>
+      <c r="B22" s="7" t="str">
+        <v>Relentless Pursuit</v>
+      </c>
+      <c r="C22" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D22" s="7" t="str">
+        <v>IMP-01</v>
+      </c>
+      <c r="E22" s="7" t="str">
+        <v>movement</v>
+      </c>
+      <c r="F22" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G22" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H22" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#imp-01-e02</v>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1">
+      <c r="A23" s="7" t="str">
+        <v>IMP-01-E03</v>
+      </c>
+      <c r="B23" s="7" t="str">
+        <v>Piercing Charge</v>
+      </c>
+      <c r="C23" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D23" s="7" t="str">
+        <v>IMP-01</v>
+      </c>
+      <c r="E23" s="7" t="str">
+        <v>movement</v>
+      </c>
+      <c r="F23" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G23" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H23" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#imp-01-e03</v>
+      </c>
+    </row>
+    <row r="24" ht="80" customHeight="1">
+      <c r="A24" s="7" t="str">
+        <v>IMP-02</v>
+      </c>
+      <c r="B24" s="7" t="str">
+        <v>Arc Strike</v>
+      </c>
+      <c r="C24" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D24" s="7" t="str"/>
+      <c r="E24" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F24" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G24" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H24" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#imp-02</v>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1">
+      <c r="A25" s="7" t="str">
+        <v>IMP-02-E01</v>
+      </c>
+      <c r="B25" s="7" t="str">
+        <v>Twin Arc</v>
+      </c>
+      <c r="C25" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D25" s="7" t="str">
+        <v>IMP-02</v>
+      </c>
+      <c r="E25" s="7" t="str">
+        <v>area, timing</v>
+      </c>
+      <c r="F25" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G25" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H25" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#imp-02-e01</v>
+      </c>
+    </row>
+    <row r="26" ht="80" customHeight="1">
+      <c r="A26" s="7" t="str">
+        <v>IMP-02-E02</v>
+      </c>
+      <c r="B26" s="7" t="str">
+        <v>Overdrive</v>
+      </c>
+      <c r="C26" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D26" s="7" t="str">
+        <v>IMP-02</v>
+      </c>
+      <c r="E26" s="7" t="str">
+        <v>timing</v>
+      </c>
+      <c r="F26" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G26" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H26" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#imp-02-e02</v>
+      </c>
+    </row>
+    <row r="27" ht="80" customHeight="1">
+      <c r="A27" s="7" t="str">
+        <v>IMP-02-E03</v>
+      </c>
+      <c r="B27" s="7" t="str">
+        <v>Kinetic Reprisal</v>
+      </c>
+      <c r="C27" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D27" s="7" t="str">
+        <v>IMP-02</v>
+      </c>
+      <c r="E27" s="7" t="str">
+        <v>protection</v>
+      </c>
+      <c r="F27" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G27" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H27" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#imp-02-e03</v>
+      </c>
+    </row>
+    <row r="28" ht="80" customHeight="1">
+      <c r="A28" s="7" t="str">
+        <v>IMP-03</v>
+      </c>
+      <c r="B28" s="7" t="str">
+        <v>Pulse Sever</v>
+      </c>
+      <c r="C28" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D28" s="7" t="str"/>
+      <c r="E28" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F28" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G28" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H28" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#imp-03</v>
+      </c>
+    </row>
+    <row r="29" ht="80" customHeight="1">
+      <c r="A29" s="7" t="str">
+        <v>IMP-03-E01</v>
+      </c>
+      <c r="B29" s="7" t="str">
+        <v>Echo Sever</v>
+      </c>
+      <c r="C29" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D29" s="7" t="str">
+        <v>IMP-03</v>
+      </c>
+      <c r="E29" s="7" t="str">
+        <v>control, area, timing</v>
+      </c>
+      <c r="F29" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G29" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H29" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#imp-03-e01</v>
+      </c>
+    </row>
+    <row r="30" ht="80" customHeight="1">
+      <c r="A30" s="7" t="str">
+        <v>IMP-03-E02</v>
+      </c>
+      <c r="B30" s="7" t="str">
+        <v>Countershock</v>
+      </c>
+      <c r="C30" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D30" s="7" t="str">
+        <v>IMP-03</v>
+      </c>
+      <c r="E30" s="7" t="str">
+        <v>control</v>
+      </c>
+      <c r="F30" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G30" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H30" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#imp-03-e02</v>
+      </c>
+    </row>
+    <row r="31" ht="80" customHeight="1">
+      <c r="A31" s="7" t="str">
+        <v>IMP-03-E03</v>
+      </c>
+      <c r="B31" s="7" t="str">
+        <v>Warpath</v>
+      </c>
+      <c r="C31" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D31" s="7" t="str">
+        <v>IMP-03</v>
+      </c>
+      <c r="E31" s="7" t="str">
+        <v>control</v>
+      </c>
+      <c r="F31" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G31" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H31" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#imp-03-e03</v>
+      </c>
+    </row>
+    <row r="32" ht="80" customHeight="1">
+      <c r="A32" s="7" t="str">
+        <v>IMP-04</v>
+      </c>
+      <c r="B32" s="7" t="str">
+        <v>Gravity Hammer</v>
+      </c>
+      <c r="C32" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D32" s="7" t="str"/>
+      <c r="E32" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F32" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G32" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H32" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#imp-04</v>
+      </c>
+    </row>
+    <row r="33" ht="80" customHeight="1">
+      <c r="A33" s="7" t="str">
+        <v>IMP-04-E01</v>
+      </c>
+      <c r="B33" s="7" t="str">
+        <v>Singularity Impact</v>
+      </c>
+      <c r="C33" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D33" s="7" t="str">
+        <v>IMP-04</v>
+      </c>
+      <c r="E33" s="7" t="str">
+        <v>area</v>
+      </c>
+      <c r="F33" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G33" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H33" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#imp-04-e01</v>
+      </c>
+    </row>
+    <row r="34" ht="80" customHeight="1">
+      <c r="A34" s="7" t="str">
+        <v>IMP-04-E02</v>
+      </c>
+      <c r="B34" s="7" t="str">
+        <v>Seismic Wave</v>
+      </c>
+      <c r="C34" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D34" s="7" t="str">
+        <v>IMP-04</v>
+      </c>
+      <c r="E34" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F34" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G34" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H34" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#imp-04-e02</v>
+      </c>
+    </row>
+    <row r="35" ht="80" customHeight="1">
+      <c r="A35" s="7" t="str">
+        <v>IMP-04-E03</v>
+      </c>
+      <c r="B35" s="7" t="str">
+        <v>Gravity Well</v>
+      </c>
+      <c r="C35" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D35" s="7" t="str">
+        <v>IMP-04</v>
+      </c>
+      <c r="E35" s="7" t="str">
+        <v>area</v>
+      </c>
+      <c r="F35" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G35" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H35" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#imp-04-e03</v>
+      </c>
+    </row>
+    <row r="36" ht="80" customHeight="1">
+      <c r="A36" s="7" t="str">
+        <v>IMP-05</v>
+      </c>
+      <c r="B36" s="7" t="str">
+        <v>Seismic Uppercut</v>
+      </c>
+      <c r="C36" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D36" s="7" t="str"/>
+      <c r="E36" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F36" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G36" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H36" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#imp-05</v>
+      </c>
+    </row>
+    <row r="37" ht="80" customHeight="1">
+      <c r="A37" s="7" t="str">
+        <v>IMP-06</v>
+      </c>
+      <c r="B37" s="7" t="str">
+        <v>Kinetic Rampart</v>
+      </c>
+      <c r="C37" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D37" s="7" t="str"/>
+      <c r="E37" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F37" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G37" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H37" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#imp-06</v>
+      </c>
+    </row>
+    <row r="38" ht="80" customHeight="1">
+      <c r="A38" s="7" t="str">
+        <v>ECL-01</v>
+      </c>
+      <c r="B38" s="7" t="str">
+        <v>Crystal Bolt</v>
+      </c>
+      <c r="C38" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D38" s="7" t="str"/>
+      <c r="E38" s="7" t="str">
+        <v>projectile</v>
+      </c>
+      <c r="F38" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G38" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H38" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#ecl-01</v>
+      </c>
+    </row>
+    <row r="39" ht="80" customHeight="1">
+      <c r="A39" s="7" t="str">
+        <v>ECL-01-E01</v>
+      </c>
+      <c r="B39" s="7" t="str">
+        <v>Rapid Crystal</v>
+      </c>
+      <c r="C39" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D39" s="7" t="str">
+        <v>ECL-01</v>
+      </c>
+      <c r="E39" s="7" t="str">
+        <v>projectile, timing</v>
+      </c>
+      <c r="F39" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G39" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H39" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#ecl-01-e01</v>
+      </c>
+    </row>
+    <row r="40" ht="80" customHeight="1">
+      <c r="A40" s="7" t="str">
+        <v>ECL-01-E02</v>
+      </c>
+      <c r="B40" s="7" t="str">
+        <v>Glacial Echo</v>
+      </c>
+      <c r="C40" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D40" s="7" t="str">
+        <v>ECL-01</v>
+      </c>
+      <c r="E40" s="7" t="str">
+        <v>projectile</v>
+      </c>
+      <c r="F40" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G40" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H40" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#ecl-01-e02</v>
+      </c>
+    </row>
+    <row r="41" ht="80" customHeight="1">
+      <c r="A41" s="7" t="str">
+        <v>ECL-01-E03</v>
+      </c>
+      <c r="B41" s="7" t="str">
+        <v>Fracture Chain</v>
+      </c>
+      <c r="C41" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D41" s="7" t="str">
+        <v>ECL-01</v>
+      </c>
+      <c r="E41" s="7" t="str">
+        <v>projectile, area, timing</v>
+      </c>
+      <c r="F41" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G41" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H41" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#ecl-01-e03</v>
+      </c>
+    </row>
+    <row r="42" ht="80" customHeight="1">
+      <c r="A42" s="7" t="str">
+        <v>ECL-02</v>
+      </c>
+      <c r="B42" s="7" t="str">
+        <v>Crystal Snare</v>
+      </c>
+      <c r="C42" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D42" s="7" t="str"/>
+      <c r="E42" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F42" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G42" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H42" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#ecl-02</v>
+      </c>
+    </row>
+    <row r="43" ht="80" customHeight="1">
+      <c r="A43" s="7" t="str">
+        <v>ECL-02-E01</v>
+      </c>
+      <c r="B43" s="7" t="str">
+        <v>Deep Freeze / Ice Tomb</v>
+      </c>
+      <c r="C43" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D43" s="7" t="str">
+        <v>ECL-02</v>
+      </c>
+      <c r="E43" s="7" t="str">
+        <v>control, area</v>
+      </c>
+      <c r="F43" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G43" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H43" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#ecl-02-e01</v>
+      </c>
+    </row>
+    <row r="44" ht="80" customHeight="1">
+      <c r="A44" s="7" t="str">
+        <v>ECL-02-E02</v>
+      </c>
+      <c r="B44" s="7" t="str">
+        <v>Shatterfield</v>
+      </c>
+      <c r="C44" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D44" s="7" t="str">
+        <v>ECL-02</v>
+      </c>
+      <c r="E44" s="7" t="str">
+        <v>control, area, timing</v>
+      </c>
+      <c r="F44" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G44" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H44" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#ecl-02-e02</v>
+      </c>
+    </row>
+    <row r="45" ht="80" customHeight="1">
+      <c r="A45" s="7" t="str">
+        <v>ECL-02-E03</v>
+      </c>
+      <c r="B45" s="7" t="str">
+        <v>Crystal Conduit</v>
+      </c>
+      <c r="C45" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D45" s="7" t="str">
+        <v>ECL-02</v>
+      </c>
+      <c r="E45" s="7" t="str">
+        <v>control</v>
+      </c>
+      <c r="F45" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G45" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H45" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#ecl-02-e03</v>
+      </c>
+    </row>
+    <row r="46" ht="80" customHeight="1">
+      <c r="A46" s="7" t="str">
+        <v>ECL-03</v>
+      </c>
+      <c r="B46" s="7" t="str">
+        <v>Fracture Spear</v>
+      </c>
+      <c r="C46" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D46" s="7" t="str"/>
+      <c r="E46" s="7" t="str">
+        <v>projectile</v>
+      </c>
+      <c r="F46" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G46" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H46" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#ecl-03</v>
+      </c>
+    </row>
+    <row r="47" ht="80" customHeight="1">
+      <c r="A47" s="7" t="str">
+        <v>ECL-03-E01</v>
+      </c>
+      <c r="B47" s="7" t="str">
+        <v>Focused Fracture</v>
+      </c>
+      <c r="C47" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D47" s="7" t="str">
+        <v>ECL-03</v>
+      </c>
+      <c r="E47" s="7" t="str">
+        <v>control, projectile</v>
+      </c>
+      <c r="F47" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G47" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H47" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#ecl-03-e01</v>
+      </c>
+    </row>
+    <row r="48" ht="80" customHeight="1">
+      <c r="A48" s="7" t="str">
+        <v>ECL-03-E02</v>
+      </c>
+      <c r="B48" s="7" t="str">
+        <v>Crystal Rupture</v>
+      </c>
+      <c r="C48" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D48" s="7" t="str">
+        <v>ECL-03</v>
+      </c>
+      <c r="E48" s="7" t="str">
+        <v>projectile, area</v>
+      </c>
+      <c r="F48" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G48" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H48" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#ecl-03-e02</v>
+      </c>
+    </row>
+    <row r="49" ht="80" customHeight="1">
+      <c r="A49" s="7" t="str">
+        <v>ECL-03-E03</v>
+      </c>
+      <c r="B49" s="7" t="str">
+        <v>Riftbreaker</v>
+      </c>
+      <c r="C49" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D49" s="7" t="str">
+        <v>ECL-03</v>
+      </c>
+      <c r="E49" s="7" t="str">
+        <v>control, projectile, timing</v>
+      </c>
+      <c r="F49" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G49" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H49" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#ecl-03-e03</v>
+      </c>
+    </row>
+    <row r="50" ht="80" customHeight="1">
+      <c r="A50" s="7" t="str">
+        <v>ECL-04</v>
+      </c>
+      <c r="B50" s="7" t="str">
+        <v>Froststorm</v>
+      </c>
+      <c r="C50" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D50" s="7" t="str"/>
+      <c r="E50" s="7" t="str">
+        <v>control</v>
+      </c>
+      <c r="F50" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G50" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H50" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#ecl-04</v>
+      </c>
+    </row>
+    <row r="51" ht="80" customHeight="1">
+      <c r="A51" s="7" t="str">
+        <v>ECL-04-E01</v>
+      </c>
+      <c r="B51" s="7" t="str">
+        <v>Glacial Barrage</v>
+      </c>
+      <c r="C51" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D51" s="7" t="str">
+        <v>ECL-04</v>
+      </c>
+      <c r="E51" s="7" t="str">
+        <v>control, area</v>
+      </c>
+      <c r="F51" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G51" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H51" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#ecl-04-e01</v>
+      </c>
+    </row>
+    <row r="52" ht="80" customHeight="1">
+      <c r="A52" s="7" t="str">
+        <v>ECL-04-E02</v>
+      </c>
+      <c r="B52" s="7" t="str">
+        <v>Expanding Frost</v>
+      </c>
+      <c r="C52" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D52" s="7" t="str">
+        <v>ECL-04</v>
+      </c>
+      <c r="E52" s="7" t="str">
+        <v>control</v>
+      </c>
+      <c r="F52" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G52" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H52" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#ecl-04-e02</v>
+      </c>
+    </row>
+    <row r="53" ht="80" customHeight="1">
+      <c r="A53" s="7" t="str">
+        <v>ECL-04-E03</v>
+      </c>
+      <c r="B53" s="7" t="str">
+        <v>Shattering Storm</v>
+      </c>
+      <c r="C53" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D53" s="7" t="str">
+        <v>ECL-04</v>
+      </c>
+      <c r="E53" s="7" t="str">
+        <v>control, projectile, area</v>
+      </c>
+      <c r="F53" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G53" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H53" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#ecl-04-e03</v>
+      </c>
+    </row>
+    <row r="54" ht="80" customHeight="1">
+      <c r="A54" s="7" t="str">
+        <v>ECL-05</v>
+      </c>
+      <c r="B54" s="7" t="str">
+        <v>Crystal Mirror</v>
+      </c>
+      <c r="C54" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D54" s="7" t="str"/>
+      <c r="E54" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F54" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G54" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H54" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#ecl-05</v>
+      </c>
+    </row>
+    <row r="55" ht="80" customHeight="1">
+      <c r="A55" s="7" t="str">
+        <v>ECL-06</v>
+      </c>
+      <c r="B55" s="7" t="str">
+        <v>Avalanche</v>
+      </c>
+      <c r="C55" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D55" s="7" t="str"/>
+      <c r="E55" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F55" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G55" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H55" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#ecl-06</v>
+      </c>
+    </row>
+    <row r="56" ht="80" customHeight="1">
+      <c r="A56" s="7" t="str">
+        <v>SOL-01</v>
+      </c>
+      <c r="B56" s="7" t="str">
+        <v>Flux Bolt</v>
+      </c>
+      <c r="C56" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D56" s="7" t="str"/>
+      <c r="E56" s="7" t="str">
+        <v>projectile</v>
+      </c>
+      <c r="F56" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G56" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H56" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#sol-01</v>
+      </c>
+    </row>
+    <row r="57" ht="80" customHeight="1">
+      <c r="A57" s="7" t="str">
+        <v>SOL-01-E01</v>
+      </c>
+      <c r="B57" s="7" t="str">
+        <v>Corona Volley</v>
+      </c>
+      <c r="C57" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D57" s="7" t="str">
+        <v>SOL-01</v>
+      </c>
+      <c r="E57" s="7" t="str">
+        <v>projectile, timing</v>
+      </c>
+      <c r="F57" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G57" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H57" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#sol-01-e01</v>
+      </c>
+    </row>
+    <row r="58" ht="80" customHeight="1">
+      <c r="A58" s="7" t="str">
+        <v>SOL-01-E02</v>
+      </c>
+      <c r="B58" s="7" t="str">
+        <v>Thunderhead</v>
+      </c>
+      <c r="C58" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D58" s="7" t="str">
+        <v>SOL-01</v>
+      </c>
+      <c r="E58" s="7" t="str">
+        <v>projectile, timing</v>
+      </c>
+      <c r="F58" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G58" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H58" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#sol-01-e02</v>
+      </c>
+    </row>
+    <row r="59" ht="80" customHeight="1">
+      <c r="A59" s="7" t="str">
+        <v>SOL-01-E03</v>
+      </c>
+      <c r="B59" s="7" t="str">
+        <v>Helios Beam</v>
+      </c>
+      <c r="C59" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D59" s="7" t="str">
+        <v>SOL-01</v>
+      </c>
+      <c r="E59" s="7" t="str">
+        <v>projectile, beam, timing</v>
+      </c>
+      <c r="F59" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G59" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H59" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#sol-01-e03</v>
+      </c>
+    </row>
+    <row r="60" ht="80" customHeight="1">
+      <c r="A60" s="7" t="str">
+        <v>SOL-02</v>
+      </c>
+      <c r="B60" s="7" t="str">
+        <v>Sun Lance</v>
+      </c>
+      <c r="C60" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D60" s="7" t="str"/>
+      <c r="E60" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F60" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G60" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H60" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#sol-02</v>
+      </c>
+    </row>
+    <row r="61" ht="80" customHeight="1">
+      <c r="A61" s="7" t="str">
+        <v>SOL-02-E01</v>
+      </c>
+      <c r="B61" s="7" t="str">
+        <v>Judgment of Dawn</v>
+      </c>
+      <c r="C61" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D61" s="7" t="str">
+        <v>SOL-02</v>
+      </c>
+      <c r="E61" s="7" t="str">
+        <v>healing, beam</v>
+      </c>
+      <c r="F61" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G61" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H61" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#sol-02-e01</v>
+      </c>
+    </row>
+    <row r="62" ht="80" customHeight="1">
+      <c r="A62" s="7" t="str">
+        <v>SOL-02-E02</v>
+      </c>
+      <c r="B62" s="7" t="str">
+        <v>Scorching Lance</v>
+      </c>
+      <c r="C62" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D62" s="7" t="str">
+        <v>SOL-02</v>
+      </c>
+      <c r="E62" s="7" t="str">
+        <v>area, periodic</v>
+      </c>
+      <c r="F62" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G62" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H62" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#sol-02-e02</v>
+      </c>
+    </row>
+    <row r="63" ht="80" customHeight="1">
+      <c r="A63" s="7" t="str">
+        <v>SOL-02-E03</v>
+      </c>
+      <c r="B63" s="7" t="str">
+        <v>Split Lance</v>
+      </c>
+      <c r="C63" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D63" s="7" t="str">
+        <v>SOL-02</v>
+      </c>
+      <c r="E63" s="7" t="str">
+        <v>area</v>
+      </c>
+      <c r="F63" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G63" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H63" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#sol-02-e03</v>
+      </c>
+    </row>
+    <row r="64" ht="80" customHeight="1">
+      <c r="A64" s="7" t="str">
+        <v>SOL-03</v>
+      </c>
+      <c r="B64" s="7" t="str">
+        <v>Zenith Crash</v>
+      </c>
+      <c r="C64" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D64" s="7" t="str"/>
+      <c r="E64" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F64" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G64" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H64" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#sol-03</v>
+      </c>
+    </row>
+    <row r="65" ht="80" customHeight="1">
+      <c r="A65" s="7" t="str">
+        <v>SOL-03-E01</v>
+      </c>
+      <c r="B65" s="7" t="str">
+        <v>Solar Aftershock</v>
+      </c>
+      <c r="C65" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D65" s="7" t="str">
+        <v>SOL-03</v>
+      </c>
+      <c r="E65" s="7" t="str">
+        <v>area</v>
+      </c>
+      <c r="F65" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G65" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H65" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#sol-03-e01</v>
+      </c>
+    </row>
+    <row r="66" ht="80" customHeight="1">
+      <c r="A66" s="7" t="str">
+        <v>SOL-03-E02</v>
+      </c>
+      <c r="B66" s="7" t="str">
+        <v>Burning Ground</v>
+      </c>
+      <c r="C66" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D66" s="7" t="str">
+        <v>SOL-03</v>
+      </c>
+      <c r="E66" s="7" t="str">
+        <v>area, periodic</v>
+      </c>
+      <c r="F66" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G66" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H66" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#sol-03-e02</v>
+      </c>
+    </row>
+    <row r="67" ht="80" customHeight="1">
+      <c r="A67" s="7" t="str">
+        <v>SOL-03-E03</v>
+      </c>
+      <c r="B67" s="7" t="str">
+        <v>Prism Cross</v>
+      </c>
+      <c r="C67" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D67" s="7" t="str">
+        <v>SOL-03</v>
+      </c>
+      <c r="E67" s="7" t="str">
+        <v>beam</v>
+      </c>
+      <c r="F67" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G67" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H67" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#sol-03-e03</v>
+      </c>
+    </row>
+    <row r="68" ht="80" customHeight="1">
+      <c r="A68" s="7" t="str">
+        <v>SOL-04</v>
+      </c>
+      <c r="B68" s="7" t="str">
+        <v>Cinder Familiar</v>
+      </c>
+      <c r="C68" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D68" s="7" t="str"/>
+      <c r="E68" s="7" t="str">
+        <v>summon</v>
+      </c>
+      <c r="F68" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G68" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H68" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#sol-04</v>
+      </c>
+    </row>
+    <row r="69" ht="80" customHeight="1">
+      <c r="A69" s="7" t="str">
+        <v>SOL-04-E01</v>
+      </c>
+      <c r="B69" s="7" t="str">
+        <v>Phoenix Dive</v>
+      </c>
+      <c r="C69" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D69" s="7" t="str">
+        <v>SOL-04</v>
+      </c>
+      <c r="E69" s="7" t="str">
+        <v>summon</v>
+      </c>
+      <c r="F69" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G69" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H69" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#sol-04-e01</v>
+      </c>
+    </row>
+    <row r="70" ht="80" customHeight="1">
+      <c r="A70" s="7" t="str">
+        <v>SOL-04-E02</v>
+      </c>
+      <c r="B70" s="7" t="str">
+        <v>Soulbrand</v>
+      </c>
+      <c r="C70" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D70" s="7" t="str">
+        <v>SOL-04</v>
+      </c>
+      <c r="E70" s="7" t="str">
+        <v>summon, projectile</v>
+      </c>
+      <c r="F70" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G70" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H70" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#sol-04-e02</v>
+      </c>
+    </row>
+    <row r="71" ht="80" customHeight="1">
+      <c r="A71" s="7" t="str">
+        <v>SOL-04-E03</v>
+      </c>
+      <c r="B71" s="7" t="str">
+        <v>Dying Star</v>
+      </c>
+      <c r="C71" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D71" s="7" t="str">
+        <v>SOL-04</v>
+      </c>
+      <c r="E71" s="7" t="str">
+        <v>summon, area, timing</v>
+      </c>
+      <c r="F71" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G71" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H71" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#sol-04-e03</v>
+      </c>
+    </row>
+    <row r="72" ht="80" customHeight="1">
+      <c r="A72" s="7" t="str">
+        <v>SOL-05</v>
+      </c>
+      <c r="B72" s="7" t="str">
+        <v>Solar Ascension</v>
+      </c>
+      <c r="C72" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D72" s="7" t="str"/>
+      <c r="E72" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F72" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G72" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H72" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#sol-05</v>
+      </c>
+    </row>
+    <row r="73" ht="80" customHeight="1">
+      <c r="A73" s="7" t="str">
+        <v>SOL-06</v>
+      </c>
+      <c r="B73" s="7" t="str">
+        <v>Chain Tempest</v>
+      </c>
+      <c r="C73" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D73" s="7" t="str"/>
+      <c r="E73" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F73" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G73" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H73" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#sol-06</v>
+      </c>
+    </row>
+    <row r="74" ht="80" customHeight="1">
+      <c r="A74" s="7" t="str">
+        <v>VOI-01</v>
+      </c>
+      <c r="B74" s="7" t="str">
+        <v>Rift Slash</v>
+      </c>
+      <c r="C74" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D74" s="7" t="str"/>
+      <c r="E74" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F74" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G74" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H74" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#voi-01</v>
+      </c>
+    </row>
+    <row r="75" ht="80" customHeight="1">
+      <c r="A75" s="7" t="str">
+        <v>VOI-01-E01</v>
+      </c>
+      <c r="B75" s="7" t="str">
+        <v>Phantom Assault</v>
+      </c>
+      <c r="C75" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D75" s="7" t="str">
+        <v>VOI-01</v>
+      </c>
+      <c r="E75" s="7" t="str">
+        <v>timing</v>
+      </c>
+      <c r="F75" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G75" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H75" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#voi-01-e01</v>
+      </c>
+    </row>
+    <row r="76" ht="80" customHeight="1">
+      <c r="A76" s="7" t="str">
+        <v>VOI-01-E02</v>
+      </c>
+      <c r="B76" s="7" t="str">
+        <v>Umbral Cyclone</v>
+      </c>
+      <c r="C76" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D76" s="7" t="str">
+        <v>VOI-01</v>
+      </c>
+      <c r="E76" s="7" t="str">
+        <v>area, timing</v>
+      </c>
+      <c r="F76" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G76" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H76" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#voi-01-e02</v>
+      </c>
+    </row>
+    <row r="77" ht="80" customHeight="1">
+      <c r="A77" s="7" t="str">
+        <v>VOI-01-E03</v>
+      </c>
+      <c r="B77" s="7" t="str">
+        <v>Executioner's Veil</v>
+      </c>
+      <c r="C77" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D77" s="7" t="str">
+        <v>VOI-01</v>
+      </c>
+      <c r="E77" s="7" t="str">
+        <v>healing, timing</v>
+      </c>
+      <c r="F77" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G77" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H77" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#voi-01-e03</v>
+      </c>
+    </row>
+    <row r="78" ht="80" customHeight="1">
+      <c r="A78" s="7" t="str">
+        <v>VOI-02</v>
+      </c>
+      <c r="B78" s="7" t="str">
+        <v>Entropy Mark</v>
+      </c>
+      <c r="C78" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D78" s="7" t="str"/>
+      <c r="E78" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F78" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G78" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H78" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#voi-02</v>
+      </c>
+    </row>
+    <row r="79" ht="80" customHeight="1">
+      <c r="A79" s="7" t="str">
+        <v>VOI-02-E01</v>
+      </c>
+      <c r="B79" s="7" t="str">
+        <v>Contagion</v>
+      </c>
+      <c r="C79" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D79" s="7" t="str">
+        <v>VOI-02</v>
+      </c>
+      <c r="E79" s="7" t="str">
+        <v>area</v>
+      </c>
+      <c r="F79" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G79" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H79" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#voi-02-e01</v>
+      </c>
+    </row>
+    <row r="80" ht="80" customHeight="1">
+      <c r="A80" s="7" t="str">
+        <v>VOI-02-E02</v>
+      </c>
+      <c r="B80" s="7" t="str">
+        <v>Psychic Collapse</v>
+      </c>
+      <c r="C80" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D80" s="7" t="str">
+        <v>VOI-02</v>
+      </c>
+      <c r="E80" s="7" t="str">
+        <v>area, timing</v>
+      </c>
+      <c r="F80" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G80" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H80" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#voi-02-e02</v>
+      </c>
+    </row>
+    <row r="81" ht="80" customHeight="1">
+      <c r="A81" s="7" t="str">
+        <v>VOI-02-E03</v>
+      </c>
+      <c r="B81" s="7" t="str">
+        <v>Devouring Pact</v>
+      </c>
+      <c r="C81" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D81" s="7" t="str">
+        <v>VOI-02</v>
+      </c>
+      <c r="E81" s="7" t="str">
+        <v>healing</v>
+      </c>
+      <c r="F81" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G81" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H81" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#voi-02-e03</v>
+      </c>
+    </row>
+    <row r="82" ht="80" customHeight="1">
+      <c r="A82" s="7" t="str">
+        <v>VOI-03</v>
+      </c>
+      <c r="B82" s="7" t="str">
+        <v>Phase Slip</v>
+      </c>
+      <c r="C82" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D82" s="7" t="str"/>
+      <c r="E82" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F82" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G82" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H82" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#voi-03</v>
+      </c>
+    </row>
+    <row r="83" ht="80" customHeight="1">
+      <c r="A83" s="7" t="str">
+        <v>VOI-03-E01</v>
+      </c>
+      <c r="B83" s="7" t="str">
+        <v>Shadow Ambush</v>
+      </c>
+      <c r="C83" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D83" s="7" t="str">
+        <v>VOI-03</v>
+      </c>
+      <c r="E83" s="7" t="str">
+        <v>timing</v>
+      </c>
+      <c r="F83" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G83" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H83" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#voi-03-e01</v>
+      </c>
+    </row>
+    <row r="84" ht="80" customHeight="1">
+      <c r="A84" s="7" t="str">
+        <v>VOI-03-E02</v>
+      </c>
+      <c r="B84" s="7" t="str">
+        <v>Rift Echo</v>
+      </c>
+      <c r="C84" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D84" s="7" t="str">
+        <v>VOI-03</v>
+      </c>
+      <c r="E84" s="7" t="str">
+        <v>movement, area, timing</v>
+      </c>
+      <c r="F84" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G84" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H84" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#voi-03-e02</v>
+      </c>
+    </row>
+    <row r="85" ht="80" customHeight="1">
+      <c r="A85" s="7" t="str">
+        <v>VOI-03-E03</v>
+      </c>
+      <c r="B85" s="7" t="str">
+        <v>Veilwalk</v>
+      </c>
+      <c r="C85" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D85" s="7" t="str">
+        <v>VOI-03</v>
+      </c>
+      <c r="E85" s="7" t="str">
+        <v>protection</v>
+      </c>
+      <c r="F85" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G85" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H85" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#voi-03-e03</v>
+      </c>
+    </row>
+    <row r="86" ht="80" customHeight="1">
+      <c r="A86" s="7" t="str">
+        <v>VOI-04</v>
+      </c>
+      <c r="B86" s="7" t="str">
+        <v>Void Metamorphosis</v>
+      </c>
+      <c r="C86" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D86" s="7" t="str"/>
+      <c r="E86" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F86" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G86" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H86" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#voi-04</v>
+      </c>
+    </row>
+    <row r="87" ht="80" customHeight="1">
+      <c r="A87" s="7" t="str">
+        <v>VOI-04-E01</v>
+      </c>
+      <c r="B87" s="7" t="str">
+        <v>Dreadblade Form</v>
+      </c>
+      <c r="C87" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D87" s="7" t="str">
+        <v>VOI-04</v>
+      </c>
+      <c r="E87" s="7" t="str">
+        <v>area, timing</v>
+      </c>
+      <c r="F87" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G87" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H87" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#voi-04-e01</v>
+      </c>
+    </row>
+    <row r="88" ht="80" customHeight="1">
+      <c r="A88" s="7" t="str">
+        <v>VOI-04-E02</v>
+      </c>
+      <c r="B88" s="7" t="str">
+        <v>Mindstorm</v>
+      </c>
+      <c r="C88" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D88" s="7" t="str">
+        <v>VOI-04</v>
+      </c>
+      <c r="E88" s="7" t="str">
+        <v>projectile</v>
+      </c>
+      <c r="F88" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G88" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H88" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#voi-04-e02</v>
+      </c>
+    </row>
+    <row r="89" ht="80" customHeight="1">
+      <c r="A89" s="7" t="str">
+        <v>VOI-04-E03</v>
+      </c>
+      <c r="B89" s="7" t="str">
+        <v>Soul Devourer</v>
+      </c>
+      <c r="C89" s="7" t="str">
+        <v>evolution</v>
+      </c>
+      <c r="D89" s="7" t="str">
+        <v>VOI-04</v>
+      </c>
+      <c r="E89" s="7" t="str">
+        <v>healing</v>
+      </c>
+      <c r="F89" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G89" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H89" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#voi-04-e03</v>
+      </c>
+    </row>
+    <row r="90" ht="80" customHeight="1">
+      <c r="A90" s="7" t="str">
+        <v>VOI-05</v>
+      </c>
+      <c r="B90" s="7" t="str">
+        <v>Abyssal Rift</v>
+      </c>
+      <c r="C90" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D90" s="7" t="str"/>
+      <c r="E90" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F90" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G90" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H90" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#voi-05</v>
+      </c>
+    </row>
+    <row r="91" ht="80" customHeight="1">
+      <c r="A91" s="7" t="str">
+        <v>VOI-06</v>
+      </c>
+      <c r="B91" s="7" t="str">
+        <v>Dark Pact</v>
+      </c>
+      <c r="C91" s="7" t="str">
+        <v>base</v>
+      </c>
+      <c r="D91" s="7" t="str"/>
+      <c r="E91" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F91" s="7" t="str">
+        <v>Chris / Project Energy</v>
+      </c>
+      <c r="G91" s="7" t="str">
+        <v>Source reference; JAC adaptation draft</v>
+      </c>
+      <c r="H91" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#voi-06</v>
+      </c>
+    </row>
+    <row r="92" ht="80" customHeight="1">
+      <c r="A92" s="7" t="str">
+        <v>C01</v>
+      </c>
+      <c r="B92" s="7" t="str">
+        <v>Entropy Mark → Rift Slash + Devouring Pact</v>
+      </c>
+      <c r="C92" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D92" s="7" t="str">
+        <v>VOI-01, VOI-02, VOI-02-E03</v>
+      </c>
+      <c r="E92" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F92" s="7" t="str">
+        <v>Project Energy source combo / PR #12 curation</v>
+      </c>
+      <c r="G92" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H92" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c01</v>
+      </c>
+    </row>
+    <row r="93" ht="80" customHeight="1">
+      <c r="A93" s="7" t="str">
+        <v>C02</v>
+      </c>
+      <c r="B93" s="7" t="str">
+        <v>Entropy Mark → Psychic Collapse</v>
+      </c>
+      <c r="C93" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D93" s="7" t="str">
+        <v>VOI-02, VOI-02-E02</v>
+      </c>
+      <c r="E93" s="7" t="str">
+        <v>periodic, timing</v>
+      </c>
+      <c r="F93" s="7" t="str">
+        <v>Project Energy source combo / PR #12 curation</v>
+      </c>
+      <c r="G93" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H93" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c02</v>
+      </c>
+    </row>
+    <row r="94" ht="80" customHeight="1">
+      <c r="A94" s="7" t="str">
+        <v>C03</v>
+      </c>
+      <c r="B94" s="7" t="str">
+        <v>Phase Slip → Shadow Ambush + Rift Slash</v>
+      </c>
+      <c r="C94" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D94" s="7" t="str">
+        <v>VOI-01, VOI-03, VOI-03-E01, JAC-M047</v>
+      </c>
+      <c r="E94" s="7" t="str">
+        <v>movement</v>
+      </c>
+      <c r="F94" s="7" t="str">
+        <v>Project Energy source combo / PR #12 curation</v>
+      </c>
+      <c r="G94" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H94" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c03</v>
+      </c>
+    </row>
+    <row r="95" ht="80" customHeight="1">
+      <c r="A95" s="7" t="str">
+        <v>C04</v>
+      </c>
+      <c r="B95" s="7" t="str">
+        <v>Void Metamorphosis → Entropy Mark + Mindstorm</v>
+      </c>
+      <c r="C95" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D95" s="7" t="str">
+        <v>VOI-02, VOI-04, VOI-04-E02</v>
+      </c>
+      <c r="E95" s="7" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="F95" s="7" t="str">
+        <v>Project Energy source combo / PR #12 curation</v>
+      </c>
+      <c r="G95" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H95" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c04</v>
+      </c>
+    </row>
+    <row r="96" ht="80" customHeight="1">
+      <c r="A96" s="7" t="str">
+        <v>C05</v>
+      </c>
+      <c r="B96" s="7" t="str">
+        <v>Flux Bolt → Thunderhead</v>
+      </c>
+      <c r="C96" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D96" s="7" t="str">
+        <v>SOL-01, SOL-01-E02</v>
+      </c>
+      <c r="E96" s="7" t="str">
+        <v>projectile</v>
+      </c>
+      <c r="F96" s="7" t="str">
+        <v>Project Energy source combo / PR #12 curation</v>
+      </c>
+      <c r="G96" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H96" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c05</v>
+      </c>
+    </row>
+    <row r="97" ht="80" customHeight="1">
+      <c r="A97" s="7" t="str">
+        <v>C06</v>
+      </c>
+      <c r="B97" s="7" t="str">
+        <v>Cinder Familiar → Soulbrand + Flux Bolt</v>
+      </c>
+      <c r="C97" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D97" s="7" t="str">
+        <v>SOL-01, SOL-04, SOL-04-E02</v>
+      </c>
+      <c r="E97" s="7" t="str">
+        <v>summon, projectile</v>
+      </c>
+      <c r="F97" s="7" t="str">
+        <v>Project Energy source combo / PR #12 curation</v>
+      </c>
+      <c r="G97" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H97" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c06</v>
+      </c>
+    </row>
+    <row r="98" ht="80" customHeight="1">
+      <c r="A98" s="7" t="str">
+        <v>C07</v>
+      </c>
+      <c r="B98" s="7" t="str">
+        <v>Solar Ascension → Sun Lance / Judgment of Dawn</v>
+      </c>
+      <c r="C98" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D98" s="7" t="str">
+        <v>SOL-02, SOL-05, SOL-02-E01</v>
+      </c>
+      <c r="E98" s="7" t="str">
+        <v>movement</v>
+      </c>
+      <c r="F98" s="7" t="str">
+        <v>Project Energy source combo / PR #12 curation</v>
+      </c>
+      <c r="G98" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H98" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c07</v>
+      </c>
+    </row>
+    <row r="99" ht="80" customHeight="1">
+      <c r="A99" s="7" t="str">
+        <v>C08</v>
+      </c>
+      <c r="B99" s="7" t="str">
+        <v>Crystal Snare → Fracture Spear / Focused Fracture</v>
+      </c>
+      <c r="C99" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D99" s="7" t="str">
+        <v>ECL-02, ECL-03, ECL-03-E01</v>
+      </c>
+      <c r="E99" s="7" t="str">
+        <v>control, projectile, timing</v>
+      </c>
+      <c r="F99" s="7" t="str">
+        <v>Project Energy source combo / PR #12 curation</v>
+      </c>
+      <c r="G99" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H99" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c08</v>
+      </c>
+    </row>
+    <row r="100" ht="80" customHeight="1">
+      <c r="A100" s="7" t="str">
+        <v>C09</v>
+      </c>
+      <c r="B100" s="7" t="str">
+        <v>Froststorm → Fracture Spear / Shattering Storm</v>
+      </c>
+      <c r="C100" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D100" s="7" t="str">
+        <v>ECL-03, ECL-04, ECL-04-E03</v>
+      </c>
+      <c r="E100" s="7" t="str">
+        <v>control, projectile, area</v>
+      </c>
+      <c r="F100" s="7" t="str">
+        <v>Project Energy source combo / PR #12 curation</v>
+      </c>
+      <c r="G100" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H100" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c09</v>
+      </c>
+    </row>
+    <row r="101" ht="80" customHeight="1">
+      <c r="A101" s="7" t="str">
+        <v>C10</v>
+      </c>
+      <c r="B101" s="7" t="str">
+        <v>Phase Rush → Pulse Sever</v>
+      </c>
+      <c r="C101" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D101" s="7" t="str">
+        <v>IMP-01, IMP-03</v>
+      </c>
+      <c r="E101" s="7" t="str">
+        <v>movement, control, timing</v>
+      </c>
+      <c r="F101" s="7" t="str">
+        <v>JAC proposal / PR #12</v>
+      </c>
+      <c r="G101" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H101" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c10</v>
+      </c>
+    </row>
+    <row r="102" ht="80" customHeight="1">
+      <c r="A102" s="7" t="str">
+        <v>C11</v>
+      </c>
+      <c r="B102" s="7" t="str">
+        <v>Pulse Sever / Warpath → Arc Strike / Overdrive</v>
+      </c>
+      <c r="C102" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D102" s="7" t="str">
+        <v>IMP-02, IMP-03, IMP-02-E02, IMP-03-E03</v>
+      </c>
+      <c r="E102" s="7" t="str">
+        <v>control</v>
+      </c>
+      <c r="F102" s="7" t="str">
+        <v>JAC proposal / PR #12</v>
+      </c>
+      <c r="G102" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H102" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c11</v>
+      </c>
+    </row>
+    <row r="103" ht="80" customHeight="1">
+      <c r="A103" s="7" t="str">
+        <v>C12</v>
+      </c>
+      <c r="B103" s="7" t="str">
+        <v>Gravity Hammer / Gravity Well → Zenith Crash</v>
+      </c>
+      <c r="C103" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D103" s="7" t="str">
+        <v>IMP-04, SOL-03, IMP-04-E03</v>
+      </c>
+      <c r="E103" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F103" s="7" t="str">
+        <v>JAC proposal / PR #12</v>
+      </c>
+      <c r="G103" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H103" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c12</v>
+      </c>
+    </row>
+    <row r="104" ht="80" customHeight="1">
+      <c r="A104" s="7" t="str">
+        <v>C13</v>
+      </c>
+      <c r="B104" s="7" t="str">
+        <v>Pulse Mend / Vital Reversal → Resonance Guard</v>
+      </c>
+      <c r="C104" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D104" s="7" t="str">
+        <v>GEN-01, GEN-02, GEN-01-E03</v>
+      </c>
+      <c r="E104" s="7" t="str">
+        <v>healing, protection</v>
+      </c>
+      <c r="F104" s="7" t="str">
+        <v>Project Energy source combo / PR #12 curation</v>
+      </c>
+      <c r="G104" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H104" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c13</v>
+      </c>
+    </row>
+    <row r="105" ht="80" customHeight="1">
+      <c r="A105" s="7" t="str">
+        <v>C14</v>
+      </c>
+      <c r="B105" s="7" t="str">
+        <v>Soul Relay → Pulse Mend</v>
+      </c>
+      <c r="C105" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D105" s="7" t="str">
+        <v>GEN-01, GEN-06</v>
+      </c>
+      <c r="E105" s="7" t="str">
+        <v>healing</v>
+      </c>
+      <c r="F105" s="7" t="str">
+        <v>Project Energy source combo / PR #12 curation</v>
+      </c>
+      <c r="G105" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H105" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c14</v>
+      </c>
+    </row>
+    <row r="106" ht="80" customHeight="1">
+      <c r="A106" s="7" t="str">
+        <v>C15</v>
+      </c>
+      <c r="B106" s="7" t="str">
+        <v>Vital Recall → Resonance Guard</v>
+      </c>
+      <c r="C106" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D106" s="7" t="str">
+        <v>GEN-02, GEN-05</v>
+      </c>
+      <c r="E106" s="7" t="str">
+        <v>healing, protection</v>
+      </c>
+      <c r="F106" s="7" t="str">
+        <v>Project Energy source combo / PR #12 curation</v>
+      </c>
+      <c r="G106" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H106" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c15</v>
+      </c>
+    </row>
+    <row r="107" ht="80" customHeight="1">
+      <c r="A107" s="7" t="str">
+        <v>C16</v>
+      </c>
+      <c r="B107" s="7" t="str">
+        <v>Crystal Snare → Chain Tempest</v>
+      </c>
+      <c r="C107" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D107" s="7" t="str">
+        <v>ECL-02, SOL-06</v>
+      </c>
+      <c r="E107" s="7" t="str">
+        <v>control</v>
+      </c>
+      <c r="F107" s="7" t="str">
+        <v>JAC proposal / PR #12</v>
+      </c>
+      <c r="G107" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H107" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c16</v>
+      </c>
+    </row>
+    <row r="108" ht="80" customHeight="1">
+      <c r="A108" s="7" t="str">
+        <v>C17</v>
+      </c>
+      <c r="B108" s="7" t="str">
+        <v>Entropy Mark → Cinder Familiar / Soulbrand</v>
+      </c>
+      <c r="C108" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D108" s="7" t="str">
+        <v>SOL-04, VOI-02, SOL-04-E02</v>
+      </c>
+      <c r="E108" s="7" t="str">
+        <v>summon</v>
+      </c>
+      <c r="F108" s="7" t="str">
+        <v>JAC proposal / PR #12</v>
+      </c>
+      <c r="G108" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H108" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c17</v>
+      </c>
+    </row>
+    <row r="109" ht="80" customHeight="1">
+      <c r="A109" s="7" t="str">
+        <v>C18</v>
+      </c>
+      <c r="B109" s="7" t="str">
+        <v>Crystal Conduit → Arc Strike / Overdrive</v>
+      </c>
+      <c r="C109" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D109" s="7" t="str">
+        <v>IMP-02, IMP-02-E02, ECL-02-E03</v>
+      </c>
+      <c r="E109" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F109" s="7" t="str">
+        <v>JAC proposal / PR #12</v>
+      </c>
+      <c r="G109" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H109" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c18</v>
+      </c>
+    </row>
+    <row r="110" ht="80" customHeight="1">
+      <c r="A110" s="7" t="str">
+        <v>C19</v>
+      </c>
+      <c r="B110" s="7" t="str">
+        <v>Resonance Guard → Dark Pact</v>
+      </c>
+      <c r="C110" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D110" s="7" t="str">
+        <v>GEN-02, VOI-06</v>
+      </c>
+      <c r="E110" s="7" t="str">
+        <v>protection, timing</v>
+      </c>
+      <c r="F110" s="7" t="str">
+        <v>JAC proposal / PR #12</v>
+      </c>
+      <c r="G110" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H110" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c19</v>
+      </c>
+    </row>
+    <row r="111" ht="80" customHeight="1">
+      <c r="A111" s="7" t="str">
+        <v>C20</v>
+      </c>
+      <c r="B111" s="7" t="str">
+        <v>Crystal Mirror → Helios Beam</v>
+      </c>
+      <c r="C111" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D111" s="7" t="str">
+        <v>ECL-05, SOL-01-E03</v>
+      </c>
+      <c r="E111" s="7" t="str">
+        <v>beam, timing</v>
+      </c>
+      <c r="F111" s="7" t="str">
+        <v>JAC proposal / PR #12</v>
+      </c>
+      <c r="G111" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H111" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c20</v>
+      </c>
+    </row>
+    <row r="112" ht="80" customHeight="1">
+      <c r="A112" s="7" t="str">
+        <v>C21</v>
+      </c>
+      <c r="B112" s="7" t="str">
+        <v>Stasis Seal / Mercy Bloom → Phase Rush / Arc Strike</v>
+      </c>
+      <c r="C112" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D112" s="7" t="str">
+        <v>GEN-04, IMP-01, IMP-02, GEN-04-E02</v>
+      </c>
+      <c r="E112" s="7" t="str">
+        <v>healing</v>
+      </c>
+      <c r="F112" s="7" t="str">
+        <v>JAC proposal / PR #12</v>
+      </c>
+      <c r="G112" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H112" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c21</v>
+      </c>
+    </row>
+    <row r="113" ht="80" customHeight="1">
+      <c r="A113" s="7" t="str">
+        <v>C22</v>
+      </c>
+      <c r="B113" s="7" t="str">
+        <v>Entropy Mark → Gravity Well / Gravity Hammer</v>
+      </c>
+      <c r="C113" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D113" s="7" t="str">
+        <v>IMP-04, VOI-02, IMP-04-E03</v>
+      </c>
+      <c r="E113" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F113" s="7" t="str">
+        <v>JAC proposal / PR #12</v>
+      </c>
+      <c r="G113" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H113" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c22</v>
+      </c>
+    </row>
+    <row r="114" ht="80" customHeight="1">
+      <c r="A114" s="7" t="str">
+        <v>C23</v>
+      </c>
+      <c r="B114" s="7" t="str">
+        <v>Flux Bolt / Thunderhead → Sun Lance / Judgment of Dawn</v>
+      </c>
+      <c r="C114" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D114" s="7" t="str">
+        <v>SOL-01, SOL-02, SOL-01-E02, SOL-02-E01</v>
+      </c>
+      <c r="E114" s="7" t="str">
+        <v>projectile</v>
+      </c>
+      <c r="F114" s="7" t="str">
+        <v>JAC proposal / PR #12</v>
+      </c>
+      <c r="G114" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H114" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c23</v>
+      </c>
+    </row>
+    <row r="115" ht="80" customHeight="1">
+      <c r="A115" s="7" t="str">
+        <v>C24</v>
+      </c>
+      <c r="B115" s="7" t="str">
+        <v>Arc Strike / Kinetic Reprisal → Phase Rush</v>
+      </c>
+      <c r="C115" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D115" s="7" t="str">
+        <v>IMP-01, IMP-02, IMP-02-E03</v>
+      </c>
+      <c r="E115" s="7" t="str">
+        <v>healing, protection, movement, control, summon, projectile, area, periodic, timing</v>
+      </c>
+      <c r="F115" s="7" t="str">
+        <v>JAC proposal / PR #12</v>
+      </c>
+      <c r="G115" s="7" t="str">
+        <v>Draft combination</v>
+      </c>
+      <c r="H115" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#c24</v>
+      </c>
+    </row>
+    <row r="116" ht="80" customHeight="1">
+      <c r="A116" s="7" t="str">
+        <v>JAC-M001</v>
+      </c>
+      <c r="B116" s="7" t="str">
+        <v>Serrated Cleave</v>
+      </c>
+      <c r="C116" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D116" s="7" t="str">
+        <v>JAC-B01</v>
+      </c>
+      <c r="E116" s="7" t="str">
+        <v>area, periodic</v>
+      </c>
+      <c r="F116" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G116" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H116" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m001</v>
+      </c>
+    </row>
+    <row r="117" ht="80" customHeight="1">
+      <c r="A117" s="7" t="str">
+        <v>JAC-M002</v>
+      </c>
+      <c r="B117" s="7" t="str">
+        <v>Blood Harvest</v>
+      </c>
+      <c r="C117" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D117" s="7" t="str">
+        <v>JAC-B01</v>
+      </c>
+      <c r="E117" s="7" t="str">
+        <v>healing, area, periodic, timing</v>
+      </c>
+      <c r="F117" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G117" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H117" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m002</v>
+      </c>
+    </row>
+    <row r="118" ht="80" customHeight="1">
+      <c r="A118" s="7" t="str">
+        <v>JAC-M003</v>
+      </c>
+      <c r="B118" s="7" t="str">
+        <v>Whirlwind</v>
+      </c>
+      <c r="C118" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D118" s="7" t="str">
+        <v>JAC-B01</v>
+      </c>
+      <c r="E118" s="7" t="str">
+        <v>area</v>
+      </c>
+      <c r="F118" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G118" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H118" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m003</v>
+      </c>
+    </row>
+    <row r="119" ht="80" customHeight="1">
+      <c r="A119" s="7" t="str">
+        <v>JAC-M004</v>
+      </c>
+      <c r="B119" s="7" t="str">
+        <v>Executioner's Arc</v>
+      </c>
+      <c r="C119" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D119" s="7" t="str">
+        <v>JAC-B01</v>
+      </c>
+      <c r="E119" s="7" t="str">
+        <v>projectile, area</v>
+      </c>
+      <c r="F119" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G119" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H119" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m004</v>
+      </c>
+    </row>
+    <row r="120" ht="80" customHeight="1">
+      <c r="A120" s="7" t="str">
+        <v>JAC-M005</v>
+      </c>
+      <c r="B120" s="7" t="str">
+        <v>Unstoppable Charge</v>
+      </c>
+      <c r="C120" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D120" s="7" t="str">
+        <v>JAC-B02</v>
+      </c>
+      <c r="E120" s="7" t="str">
+        <v>movement, control</v>
+      </c>
+      <c r="F120" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G120" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H120" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m005</v>
+      </c>
+    </row>
+    <row r="121" ht="80" customHeight="1">
+      <c r="A121" s="7" t="str">
+        <v>JAC-M006</v>
+      </c>
+      <c r="B121" s="7" t="str">
+        <v>Rallying Cry</v>
+      </c>
+      <c r="C121" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D121" s="7" t="str">
+        <v>JAC-B03</v>
+      </c>
+      <c r="E121" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F121" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G121" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H121" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m006</v>
+      </c>
+    </row>
+    <row r="122" ht="80" customHeight="1">
+      <c r="A122" s="7" t="str">
+        <v>JAC-M007</v>
+      </c>
+      <c r="B122" s="7" t="str">
+        <v>Shared Mend</v>
+      </c>
+      <c r="C122" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D122" s="7" t="str">
+        <v>JAC-B04</v>
+      </c>
+      <c r="E122" s="7" t="str">
+        <v>healing, area</v>
+      </c>
+      <c r="F122" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G122" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H122" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m007</v>
+      </c>
+    </row>
+    <row r="123" ht="80" customHeight="1">
+      <c r="A123" s="7" t="str">
+        <v>JAC-M008</v>
+      </c>
+      <c r="B123" s="7" t="str">
+        <v>Prayer of Renewal</v>
+      </c>
+      <c r="C123" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D123" s="7" t="str">
+        <v>JAC-B04</v>
+      </c>
+      <c r="E123" s="7" t="str">
+        <v>healing, periodic</v>
+      </c>
+      <c r="F123" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G123" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H123" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m008</v>
+      </c>
+    </row>
+    <row r="124" ht="80" customHeight="1">
+      <c r="A124" s="7" t="str">
+        <v>JAC-M009</v>
+      </c>
+      <c r="B124" s="7" t="str">
+        <v>Divine Intervention</v>
+      </c>
+      <c r="C124" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D124" s="7" t="str">
+        <v>JAC-B04</v>
+      </c>
+      <c r="E124" s="7" t="str">
+        <v>healing, timing</v>
+      </c>
+      <c r="F124" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G124" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H124" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m009</v>
+      </c>
+    </row>
+    <row r="125" ht="80" customHeight="1">
+      <c r="A125" s="7" t="str">
+        <v>JAC-M010</v>
+      </c>
+      <c r="B125" s="7" t="str">
+        <v>Purifying Light</v>
+      </c>
+      <c r="C125" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D125" s="7" t="str">
+        <v>JAC-B05</v>
+      </c>
+      <c r="E125" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F125" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G125" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H125" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m010</v>
+      </c>
+    </row>
+    <row r="126" ht="80" customHeight="1">
+      <c r="A126" s="7" t="str">
+        <v>JAC-M011</v>
+      </c>
+      <c r="B126" s="7" t="str">
+        <v>Sanctuary</v>
+      </c>
+      <c r="C126" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D126" s="7" t="str">
+        <v>JAC-B06</v>
+      </c>
+      <c r="E126" s="7" t="str">
+        <v>protection, area</v>
+      </c>
+      <c r="F126" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G126" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H126" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m011</v>
+      </c>
+    </row>
+    <row r="127" ht="80" customHeight="1">
+      <c r="A127" s="7" t="str">
+        <v>JAC-M012</v>
+      </c>
+      <c r="B127" s="7" t="str">
+        <v>Martyr's Bond</v>
+      </c>
+      <c r="C127" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D127" s="7" t="str">
+        <v>JAC-B07</v>
+      </c>
+      <c r="E127" s="7" t="str">
+        <v>healing, area</v>
+      </c>
+      <c r="F127" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G127" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H127" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m012</v>
+      </c>
+    </row>
+    <row r="128" ht="80" customHeight="1">
+      <c r="A128" s="7" t="str">
+        <v>JAC-M013</v>
+      </c>
+      <c r="B128" s="7" t="str">
+        <v>Blizzard</v>
+      </c>
+      <c r="C128" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D128" s="7" t="str">
+        <v>JAC-B08</v>
+      </c>
+      <c r="E128" s="7" t="str">
+        <v>control</v>
+      </c>
+      <c r="F128" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G128" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H128" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m013</v>
+      </c>
+    </row>
+    <row r="129" ht="80" customHeight="1">
+      <c r="A129" s="7" t="str">
+        <v>JAC-M014</v>
+      </c>
+      <c r="B129" s="7" t="str">
+        <v>Thunder Prison</v>
+      </c>
+      <c r="C129" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D129" s="7" t="str">
+        <v>JAC-B08</v>
+      </c>
+      <c r="E129" s="7" t="str">
+        <v>control, area</v>
+      </c>
+      <c r="F129" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G129" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H129" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m014</v>
+      </c>
+    </row>
+    <row r="130" ht="80" customHeight="1">
+      <c r="A130" s="7" t="str">
+        <v>JAC-M015</v>
+      </c>
+      <c r="B130" s="7" t="str">
+        <v>Storm Chaser</v>
+      </c>
+      <c r="C130" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D130" s="7" t="str">
+        <v>JAC-B08</v>
+      </c>
+      <c r="E130" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F130" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G130" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H130" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m015</v>
+      </c>
+    </row>
+    <row r="131" ht="80" customHeight="1">
+      <c r="A131" s="7" t="str">
+        <v>JAC-M016</v>
+      </c>
+      <c r="B131" s="7" t="str">
+        <v>Chain Reaction</v>
+      </c>
+      <c r="C131" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D131" s="7" t="str">
+        <v>JAC-B09</v>
+      </c>
+      <c r="E131" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F131" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G131" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H131" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m016</v>
+      </c>
+    </row>
+    <row r="132" ht="80" customHeight="1">
+      <c r="A132" s="7" t="str">
+        <v>JAC-M017</v>
+      </c>
+      <c r="B132" s="7" t="str">
+        <v>Overload</v>
+      </c>
+      <c r="C132" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D132" s="7" t="str">
+        <v>JAC-B09</v>
+      </c>
+      <c r="E132" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F132" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G132" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H132" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m017</v>
+      </c>
+    </row>
+    <row r="133" ht="80" customHeight="1">
+      <c r="A133" s="7" t="str">
+        <v>JAC-M018</v>
+      </c>
+      <c r="B133" s="7" t="str">
+        <v>Ice Block</v>
+      </c>
+      <c r="C133" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D133" s="7" t="str">
+        <v>JAC-B10</v>
+      </c>
+      <c r="E133" s="7" t="str">
+        <v>protection, movement</v>
+      </c>
+      <c r="F133" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G133" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H133" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m018</v>
+      </c>
+    </row>
+    <row r="134" ht="80" customHeight="1">
+      <c r="A134" s="7" t="str">
+        <v>JAC-M019</v>
+      </c>
+      <c r="B134" s="7" t="str">
+        <v>Static Discharge</v>
+      </c>
+      <c r="C134" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D134" s="7" t="str">
+        <v>JAC-B10</v>
+      </c>
+      <c r="E134" s="7" t="str">
+        <v>movement</v>
+      </c>
+      <c r="F134" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G134" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H134" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m019</v>
+      </c>
+    </row>
+    <row r="135" ht="80" customHeight="1">
+      <c r="A135" s="7" t="str">
+        <v>JAC-M020</v>
+      </c>
+      <c r="B135" s="7" t="str">
+        <v>Endless Volley</v>
+      </c>
+      <c r="C135" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D135" s="7" t="str">
+        <v>JAC-B11</v>
+      </c>
+      <c r="E135" s="7" t="str">
+        <v>movement, projectile, timing</v>
+      </c>
+      <c r="F135" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G135" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H135" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m020</v>
+      </c>
+    </row>
+    <row r="136" ht="80" customHeight="1">
+      <c r="A136" s="7" t="str">
+        <v>JAC-M021</v>
+      </c>
+      <c r="B136" s="7" t="str">
+        <v>Sniper's Patience</v>
+      </c>
+      <c r="C136" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D136" s="7" t="str">
+        <v>JAC-B11</v>
+      </c>
+      <c r="E136" s="7" t="str">
+        <v>movement, control</v>
+      </c>
+      <c r="F136" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G136" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H136" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m021</v>
+      </c>
+    </row>
+    <row r="137" ht="80" customHeight="1">
+      <c r="A137" s="7" t="str">
+        <v>JAC-M022</v>
+      </c>
+      <c r="B137" s="7" t="str">
+        <v>Splinter Shot</v>
+      </c>
+      <c r="C137" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D137" s="7" t="str">
+        <v>JAC-B11</v>
+      </c>
+      <c r="E137" s="7" t="str">
+        <v>projectile</v>
+      </c>
+      <c r="F137" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G137" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H137" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m022</v>
+      </c>
+    </row>
+    <row r="138" ht="80" customHeight="1">
+      <c r="A138" s="7" t="str">
+        <v>JAC-M023</v>
+      </c>
+      <c r="B138" s="7" t="str">
+        <v>Pinning Arrow</v>
+      </c>
+      <c r="C138" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D138" s="7" t="str">
+        <v>JAC-B11</v>
+      </c>
+      <c r="E138" s="7" t="str">
+        <v>movement, control, projectile</v>
+      </c>
+      <c r="F138" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G138" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H138" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m023</v>
+      </c>
+    </row>
+    <row r="139" ht="80" customHeight="1">
+      <c r="A139" s="7" t="str">
+        <v>JAC-M024</v>
+      </c>
+      <c r="B139" s="7" t="str">
+        <v>Ricochet Arrow</v>
+      </c>
+      <c r="C139" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D139" s="7" t="str">
+        <v>JAC-B11</v>
+      </c>
+      <c r="E139" s="7" t="str">
+        <v>projectile</v>
+      </c>
+      <c r="F139" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G139" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H139" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m024</v>
+      </c>
+    </row>
+    <row r="140" ht="80" customHeight="1">
+      <c r="A140" s="7" t="str">
+        <v>JAC-M025</v>
+      </c>
+      <c r="B140" s="7" t="str">
+        <v>Explosive Tip</v>
+      </c>
+      <c r="C140" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D140" s="7" t="str">
+        <v>JAC-B11</v>
+      </c>
+      <c r="E140" s="7" t="str">
+        <v>area</v>
+      </c>
+      <c r="F140" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G140" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H140" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m025</v>
+      </c>
+    </row>
+    <row r="141" ht="80" customHeight="1">
+      <c r="A141" s="7" t="str">
+        <v>JAC-M026</v>
+      </c>
+      <c r="B141" s="7" t="str">
+        <v>Rolling Escape</v>
+      </c>
+      <c r="C141" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D141" s="7" t="str">
+        <v>JAC-B10</v>
+      </c>
+      <c r="E141" s="7" t="str">
+        <v>protection, movement</v>
+      </c>
+      <c r="F141" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G141" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H141" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m026</v>
+      </c>
+    </row>
+    <row r="142" ht="80" customHeight="1">
+      <c r="A142" s="7" t="str">
+        <v>JAC-M027</v>
+      </c>
+      <c r="B142" s="7" t="str">
+        <v>Lobbed Fireball</v>
+      </c>
+      <c r="C142" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D142" s="7" t="str">
+        <v>JAC-B12</v>
+      </c>
+      <c r="E142" s="7" t="str">
+        <v>projectile</v>
+      </c>
+      <c r="F142" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G142" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H142" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m027</v>
+      </c>
+    </row>
+    <row r="143" ht="80" customHeight="1">
+      <c r="A143" s="7" t="str">
+        <v>JAC-M028</v>
+      </c>
+      <c r="B143" s="7" t="str">
+        <v>Living Flame</v>
+      </c>
+      <c r="C143" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D143" s="7" t="str">
+        <v>JAC-B12</v>
+      </c>
+      <c r="E143" s="7" t="str">
+        <v>projectile, area, periodic</v>
+      </c>
+      <c r="F143" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G143" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H143" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m028</v>
+      </c>
+    </row>
+    <row r="144" ht="80" customHeight="1">
+      <c r="A144" s="7" t="str">
+        <v>JAC-M029</v>
+      </c>
+      <c r="B144" s="7" t="str">
+        <v>Cluster Fireball</v>
+      </c>
+      <c r="C144" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D144" s="7" t="str">
+        <v>JAC-B12</v>
+      </c>
+      <c r="E144" s="7" t="str">
+        <v>projectile</v>
+      </c>
+      <c r="F144" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G144" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H144" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m029</v>
+      </c>
+    </row>
+    <row r="145" ht="80" customHeight="1">
+      <c r="A145" s="7" t="str">
+        <v>JAC-M030</v>
+      </c>
+      <c r="B145" s="7" t="str">
+        <v>Flamethrower</v>
+      </c>
+      <c r="C145" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D145" s="7" t="str">
+        <v>JAC-B12</v>
+      </c>
+      <c r="E145" s="7" t="str">
+        <v>projectile, timing</v>
+      </c>
+      <c r="F145" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G145" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H145" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m030</v>
+      </c>
+    </row>
+    <row r="146" ht="80" customHeight="1">
+      <c r="A146" s="7" t="str">
+        <v>JAC-M031</v>
+      </c>
+      <c r="B146" s="7" t="str">
+        <v>Meteor</v>
+      </c>
+      <c r="C146" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D146" s="7" t="str">
+        <v>JAC-B12</v>
+      </c>
+      <c r="E146" s="7" t="str">
+        <v>projectile, area, timing</v>
+      </c>
+      <c r="F146" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G146" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H146" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m031</v>
+      </c>
+    </row>
+    <row r="147" ht="80" customHeight="1">
+      <c r="A147" s="7" t="str">
+        <v>JAC-M032</v>
+      </c>
+      <c r="B147" s="7" t="str">
+        <v>Phoenix Dash</v>
+      </c>
+      <c r="C147" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D147" s="7" t="str">
+        <v>JAC-B10</v>
+      </c>
+      <c r="E147" s="7" t="str">
+        <v>movement, periodic</v>
+      </c>
+      <c r="F147" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G147" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H147" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m032</v>
+      </c>
+    </row>
+    <row r="148" ht="80" customHeight="1">
+      <c r="A148" s="7" t="str">
+        <v>JAC-M033</v>
+      </c>
+      <c r="B148" s="7" t="str">
+        <v>Cauterize</v>
+      </c>
+      <c r="C148" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D148" s="7" t="str">
+        <v>JAC-B13</v>
+      </c>
+      <c r="E148" s="7" t="str">
+        <v>healing</v>
+      </c>
+      <c r="F148" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G148" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H148" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m033</v>
+      </c>
+    </row>
+    <row r="149" ht="80" customHeight="1">
+      <c r="A149" s="7" t="str">
+        <v>JAC-M034</v>
+      </c>
+      <c r="B149" s="7" t="str">
+        <v>Refracting LAZOR</v>
+      </c>
+      <c r="C149" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D149" s="7" t="str">
+        <v>JAC-B14</v>
+      </c>
+      <c r="E149" s="7" t="str">
+        <v>beam</v>
+      </c>
+      <c r="F149" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G149" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H149" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m034</v>
+      </c>
+    </row>
+    <row r="150" ht="80" customHeight="1">
+      <c r="A150" s="7" t="str">
+        <v>JAC-M035</v>
+      </c>
+      <c r="B150" s="7" t="str">
+        <v>Sweeping LAZOR</v>
+      </c>
+      <c r="C150" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D150" s="7" t="str">
+        <v>JAC-B14</v>
+      </c>
+      <c r="E150" s="7" t="str">
+        <v>beam, timing</v>
+      </c>
+      <c r="F150" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G150" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H150" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m035</v>
+      </c>
+    </row>
+    <row r="151" ht="80" customHeight="1">
+      <c r="A151" s="7" t="str">
+        <v>JAC-M036</v>
+      </c>
+      <c r="B151" s="7" t="str">
+        <v>Piercing LAZOR</v>
+      </c>
+      <c r="C151" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D151" s="7" t="str">
+        <v>JAC-B14</v>
+      </c>
+      <c r="E151" s="7" t="str">
+        <v>projectile, beam</v>
+      </c>
+      <c r="F151" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G151" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H151" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m036</v>
+      </c>
+    </row>
+    <row r="152" ht="80" customHeight="1">
+      <c r="A152" s="7" t="str">
+        <v>JAC-M037</v>
+      </c>
+      <c r="B152" s="7" t="str">
+        <v>Guardian Bulwark</v>
+      </c>
+      <c r="C152" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D152" s="7" t="str">
+        <v>JAC-B15</v>
+      </c>
+      <c r="E152" s="7" t="str">
+        <v>protection, area</v>
+      </c>
+      <c r="F152" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G152" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H152" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m037</v>
+      </c>
+    </row>
+    <row r="153" ht="80" customHeight="1">
+      <c r="A153" s="7" t="str">
+        <v>JAC-M038</v>
+      </c>
+      <c r="B153" s="7" t="str">
+        <v>Reflective Bulwark</v>
+      </c>
+      <c r="C153" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D153" s="7" t="str">
+        <v>JAC-B15</v>
+      </c>
+      <c r="E153" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F153" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G153" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H153" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m038</v>
+      </c>
+    </row>
+    <row r="154" ht="80" customHeight="1">
+      <c r="A154" s="7" t="str">
+        <v>JAC-M039</v>
+      </c>
+      <c r="B154" s="7" t="str">
+        <v>Fortress Mode</v>
+      </c>
+      <c r="C154" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D154" s="7" t="str">
+        <v>JAC-B15</v>
+      </c>
+      <c r="E154" s="7" t="str">
+        <v>protection, control</v>
+      </c>
+      <c r="F154" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G154" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H154" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m039</v>
+      </c>
+    </row>
+    <row r="155" ht="80" customHeight="1">
+      <c r="A155" s="7" t="str">
+        <v>JAC-M040</v>
+      </c>
+      <c r="B155" s="7" t="str">
+        <v>Sacrificial Guard</v>
+      </c>
+      <c r="C155" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D155" s="7" t="str">
+        <v>JAC-B15</v>
+      </c>
+      <c r="E155" s="7" t="str">
+        <v>protection</v>
+      </c>
+      <c r="F155" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G155" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H155" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m040</v>
+      </c>
+    </row>
+    <row r="156" ht="80" customHeight="1">
+      <c r="A156" s="7" t="str">
+        <v>JAC-M041</v>
+      </c>
+      <c r="B156" s="7" t="str">
+        <v>Contagious Poison</v>
+      </c>
+      <c r="C156" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D156" s="7" t="str">
+        <v>JAC-B16</v>
+      </c>
+      <c r="E156" s="7" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="F156" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G156" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H156" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m041</v>
+      </c>
+    </row>
+    <row r="157" ht="80" customHeight="1">
+      <c r="A157" s="7" t="str">
+        <v>JAC-M042</v>
+      </c>
+      <c r="B157" s="7" t="str">
+        <v>Fleet Venom</v>
+      </c>
+      <c r="C157" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D157" s="7" t="str">
+        <v>JAC-B16</v>
+      </c>
+      <c r="E157" s="7" t="str">
+        <v>movement, periodic</v>
+      </c>
+      <c r="F157" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G157" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H157" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m042</v>
+      </c>
+    </row>
+    <row r="158" ht="80" customHeight="1">
+      <c r="A158" s="7" t="str">
+        <v>JAC-M043</v>
+      </c>
+      <c r="B158" s="7" t="str">
+        <v>Paralytic Venom</v>
+      </c>
+      <c r="C158" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D158" s="7" t="str">
+        <v>JAC-B17</v>
+      </c>
+      <c r="E158" s="7" t="str">
+        <v>control, periodic, timing</v>
+      </c>
+      <c r="F158" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G158" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H158" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m043</v>
+      </c>
+    </row>
+    <row r="159" ht="80" customHeight="1">
+      <c r="A159" s="7" t="str">
+        <v>JAC-M044</v>
+      </c>
+      <c r="B159" s="7" t="str">
+        <v>Explosive Venom</v>
+      </c>
+      <c r="C159" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D159" s="7" t="str">
+        <v>JAC-B18</v>
+      </c>
+      <c r="E159" s="7" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="F159" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G159" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H159" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m044</v>
+      </c>
+    </row>
+    <row r="160" ht="80" customHeight="1">
+      <c r="A160" s="7" t="str">
+        <v>JAC-M045</v>
+      </c>
+      <c r="B160" s="7" t="str">
+        <v>Shadowstep</v>
+      </c>
+      <c r="C160" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D160" s="7" t="str">
+        <v>JAC-B10</v>
+      </c>
+      <c r="E160" s="7" t="str">
+        <v>movement</v>
+      </c>
+      <c r="F160" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G160" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H160" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m045</v>
+      </c>
+    </row>
+    <row r="161" ht="80" customHeight="1">
+      <c r="A161" s="7" t="str">
+        <v>JAC-M046</v>
+      </c>
+      <c r="B161" s="7" t="str">
+        <v>Smoke Bomb</v>
+      </c>
+      <c r="C161" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D161" s="7" t="str">
+        <v>JAC-B10</v>
+      </c>
+      <c r="E161" s="7" t="str">
+        <v>movement, area</v>
+      </c>
+      <c r="F161" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G161" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H161" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m046</v>
+      </c>
+    </row>
+    <row r="162" ht="80" customHeight="1">
+      <c r="A162" s="7" t="str">
+        <v>JAC-M047</v>
+      </c>
+      <c r="B162" s="7" t="str">
+        <v>Ambush</v>
+      </c>
+      <c r="C162" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D162" s="7" t="str">
+        <v>JAC-B19</v>
+      </c>
+      <c r="E162" s="7" t="str">
+        <v>direct-effect</v>
+      </c>
+      <c r="F162" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G162" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H162" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m047</v>
+      </c>
+    </row>
+    <row r="163" ht="80" customHeight="1">
+      <c r="A163" s="7" t="str">
+        <v>JAC-M048</v>
+      </c>
+      <c r="B163" s="7" t="str">
+        <v>Totemic Legion</v>
+      </c>
+      <c r="C163" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D163" s="7" t="str">
+        <v>JAC-B20</v>
+      </c>
+      <c r="E163" s="7" t="str">
+        <v>healing, summon, timing</v>
+      </c>
+      <c r="F163" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G163" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H163" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m048</v>
+      </c>
+    </row>
+    <row r="164" ht="80" customHeight="1">
+      <c r="A164" s="7" t="str">
+        <v>JAC-M049</v>
+      </c>
+      <c r="B164" s="7" t="str">
+        <v>Ancestral Totem</v>
+      </c>
+      <c r="C164" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D164" s="7" t="str">
+        <v>JAC-B20</v>
+      </c>
+      <c r="E164" s="7" t="str">
+        <v>healing, summon, area</v>
+      </c>
+      <c r="F164" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G164" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H164" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m049</v>
+      </c>
+    </row>
+    <row r="165" ht="80" customHeight="1">
+      <c r="A165" s="7" t="str">
+        <v>JAC-M050</v>
+      </c>
+      <c r="B165" s="7" t="str">
+        <v>Spirit Link</v>
+      </c>
+      <c r="C165" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D165" s="7" t="str">
+        <v>JAC-B20</v>
+      </c>
+      <c r="E165" s="7" t="str">
+        <v>healing, summon</v>
+      </c>
+      <c r="F165" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G165" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H165" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m050</v>
+      </c>
+    </row>
+    <row r="166" ht="80" customHeight="1">
+      <c r="A166" s="7" t="str">
+        <v>JAC-M051</v>
+      </c>
+      <c r="B166" s="7" t="str">
+        <v>Volatile Totem</v>
+      </c>
+      <c r="C166" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D166" s="7" t="str">
+        <v>JAC-B21</v>
+      </c>
+      <c r="E166" s="7" t="str">
+        <v>summon</v>
+      </c>
+      <c r="F166" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G166" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H166" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m051</v>
+      </c>
+    </row>
+    <row r="167" ht="80" customHeight="1">
+      <c r="A167" s="7" t="str">
+        <v>JAC-M052</v>
+      </c>
+      <c r="B167" s="7" t="str">
+        <v>Flamecaller</v>
+      </c>
+      <c r="C167" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D167" s="7" t="str">
+        <v>JAC-B21</v>
+      </c>
+      <c r="E167" s="7" t="str">
+        <v>summon</v>
+      </c>
+      <c r="F167" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G167" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H167" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m052</v>
+      </c>
+    </row>
+    <row r="168" ht="80" customHeight="1">
+      <c r="A168" s="7" t="str">
+        <v>JAC-M053</v>
+      </c>
+      <c r="B168" s="7" t="str">
+        <v>Walking Totem</v>
+      </c>
+      <c r="C168" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D168" s="7" t="str">
+        <v>JAC-B21</v>
+      </c>
+      <c r="E168" s="7" t="str">
+        <v>summon, timing</v>
+      </c>
+      <c r="F168" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G168" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H168" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m053</v>
+      </c>
+    </row>
+    <row r="169" ht="80" customHeight="1">
+      <c r="A169" s="7" t="str">
+        <v>JAC-M054</v>
+      </c>
+      <c r="B169" s="7" t="str">
+        <v>Earthbind</v>
+      </c>
+      <c r="C169" s="7" t="str">
+        <v>mutation</v>
+      </c>
+      <c r="D169" s="7" t="str">
+        <v>JAC-B22</v>
+      </c>
+      <c r="E169" s="7" t="str">
+        <v>control, area</v>
+      </c>
+      <c r="F169" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G169" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="H169" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m054</v>
+      </c>
+    </row>
+    <row r="170" ht="80" customHeight="1">
+      <c r="A170" s="7" t="str">
+        <v>JAC-I001</v>
+      </c>
+      <c r="B170" s="7" t="str">
+        <v>Hit-absorbing skeletons</v>
+      </c>
+      <c r="C170" s="7" t="str">
+        <v>interview concept</v>
+      </c>
+      <c r="D170" s="7" t="str">
+        <v>JAC-B23</v>
+      </c>
+      <c r="E170" s="7" t="str">
+        <v>protection, summon</v>
+      </c>
+      <c r="F170" s="7" t="str">
+        <v>Axel design interview</v>
+      </c>
+      <c r="G170" s="7" t="str">
+        <v>Draft interview idea; not approved</v>
+      </c>
+      <c r="H170" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-i001</v>
+      </c>
+    </row>
+    <row r="171" ht="80" customHeight="1">
+      <c r="A171" s="7" t="str">
+        <v>JAC-I002</v>
+      </c>
+      <c r="B171" s="7" t="str">
+        <v>Melee skeletons</v>
+      </c>
+      <c r="C171" s="7" t="str">
+        <v>interview concept</v>
+      </c>
+      <c r="D171" s="7" t="str">
+        <v>JAC-B23</v>
+      </c>
+      <c r="E171" s="7" t="str">
+        <v>summon</v>
+      </c>
+      <c r="F171" s="7" t="str">
+        <v>Axel design interview</v>
+      </c>
+      <c r="G171" s="7" t="str">
+        <v>Draft interview idea; not approved</v>
+      </c>
+      <c r="H171" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-i002</v>
+      </c>
+    </row>
+    <row r="172" ht="80" customHeight="1">
+      <c r="A172" s="7" t="str">
+        <v>JAC-I003</v>
+      </c>
+      <c r="B172" s="7" t="str">
+        <v>Debuffing mage skeletons</v>
+      </c>
+      <c r="C172" s="7" t="str">
+        <v>interview concept</v>
+      </c>
+      <c r="D172" s="7" t="str">
+        <v>JAC-B23</v>
+      </c>
+      <c r="E172" s="7" t="str">
+        <v>summon</v>
+      </c>
+      <c r="F172" s="7" t="str">
+        <v>Axel design interview</v>
+      </c>
+      <c r="G172" s="7" t="str">
+        <v>Draft interview idea; not approved</v>
+      </c>
+      <c r="H172" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-i003</v>
+      </c>
+    </row>
+    <row r="173" ht="80" customHeight="1">
+      <c r="A173" s="7" t="str">
+        <v>JAC-I004</v>
+      </c>
+      <c r="B173" s="7" t="str">
+        <v>Healing skeletons</v>
+      </c>
+      <c r="C173" s="7" t="str">
+        <v>interview concept</v>
+      </c>
+      <c r="D173" s="7" t="str">
+        <v>JAC-B23</v>
+      </c>
+      <c r="E173" s="7" t="str">
+        <v>healing, summon</v>
+      </c>
+      <c r="F173" s="7" t="str">
+        <v>Axel design interview</v>
+      </c>
+      <c r="G173" s="7" t="str">
+        <v>Draft interview idea; not approved</v>
+      </c>
+      <c r="H173" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-i004</v>
+      </c>
+    </row>
+    <row r="174" ht="80" customHeight="1">
+      <c r="A174" s="7" t="str">
+        <v>JAC-I005</v>
+      </c>
+      <c r="B174" s="7" t="str">
+        <v>Hold Frostbite stacks</v>
+      </c>
+      <c r="C174" s="7" t="str">
+        <v>interview concept</v>
+      </c>
+      <c r="D174" s="7" t="str">
+        <v>JAC-B24</v>
+      </c>
+      <c r="E174" s="7" t="str">
+        <v>control, timing</v>
+      </c>
+      <c r="F174" s="7" t="str">
+        <v>Axel design interview</v>
+      </c>
+      <c r="G174" s="7" t="str">
+        <v>Draft interview idea; not approved</v>
+      </c>
+      <c r="H174" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-i005</v>
+      </c>
+    </row>
+    <row r="175" ht="80" customHeight="1">
+      <c r="A175" s="7" t="str">
+        <v>JAC-I006</v>
+      </c>
+      <c r="B175" s="7" t="str">
+        <v>Trigger Frostbite explosions</v>
+      </c>
+      <c r="C175" s="7" t="str">
+        <v>interview concept</v>
+      </c>
+      <c r="D175" s="7" t="str">
+        <v>JAC-B24</v>
+      </c>
+      <c r="E175" s="7" t="str">
+        <v>control, timing</v>
+      </c>
+      <c r="F175" s="7" t="str">
+        <v>Axel design interview</v>
+      </c>
+      <c r="G175" s="7" t="str">
+        <v>Draft interview idea; not approved</v>
+      </c>
+      <c r="H175" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-i006</v>
+      </c>
+    </row>
+    <row r="176" ht="80" customHeight="1">
+      <c r="A176" s="7" t="str">
+        <v>JAC-I007</v>
+      </c>
+      <c r="B176" s="7" t="str">
+        <v>Tactical crystal payoff</v>
+      </c>
+      <c r="C176" s="7" t="str">
+        <v>interview concept</v>
+      </c>
+      <c r="D176" s="7" t="str">
+        <v>JAC-B25</v>
+      </c>
+      <c r="E176" s="7" t="str">
+        <v>healing</v>
+      </c>
+      <c r="F176" s="7" t="str">
+        <v>Axel design interview</v>
+      </c>
+      <c r="G176" s="7" t="str">
+        <v>Draft interview idea; not approved</v>
+      </c>
+      <c r="H176" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-i007</v>
+      </c>
+    </row>
+    <row r="177" ht="80" customHeight="1">
+      <c r="A177" s="7" t="str">
+        <v>JC01</v>
+      </c>
+      <c r="B177" s="7" t="str">
+        <v>Lobbed Fireball + Living Flame</v>
+      </c>
+      <c r="C177" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D177" s="7" t="str">
+        <v>JAC-M027, JAC-M028</v>
+      </c>
+      <c r="E177" s="7" t="str">
+        <v>projectile, area, periodic</v>
+      </c>
+      <c r="F177" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G177" s="7" t="str">
+        <v>Speculative idea; not approved</v>
+      </c>
+      <c r="H177" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jc01</v>
+      </c>
+    </row>
+    <row r="178" ht="80" customHeight="1">
+      <c r="A178" s="7" t="str">
+        <v>JC02</v>
+      </c>
+      <c r="B178" s="7" t="str">
+        <v>Contagious Poison + Fleet Venom</v>
+      </c>
+      <c r="C178" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D178" s="7" t="str">
+        <v>JAC-M041, JAC-M042</v>
+      </c>
+      <c r="E178" s="7" t="str">
+        <v>movement, periodic</v>
+      </c>
+      <c r="F178" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G178" s="7" t="str">
+        <v>Speculative idea; not approved</v>
+      </c>
+      <c r="H178" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jc02</v>
+      </c>
+    </row>
+    <row r="179" ht="80" customHeight="1">
+      <c r="A179" s="7" t="str">
+        <v>JC03</v>
+      </c>
+      <c r="B179" s="7" t="str">
+        <v>Totemic Legion + Ancestral Totem</v>
+      </c>
+      <c r="C179" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D179" s="7" t="str">
+        <v>JAC-M048, JAC-M049</v>
+      </c>
+      <c r="E179" s="7" t="str">
+        <v>healing, summon, area, timing</v>
+      </c>
+      <c r="F179" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="G179" s="7" t="str">
+        <v>Speculative idea; not approved</v>
+      </c>
+      <c r="H179" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jc03</v>
+      </c>
+    </row>
+    <row r="180" ht="80" customHeight="1">
+      <c r="A180" s="7" t="str">
+        <v>H01</v>
+      </c>
+      <c r="B180" s="7" t="str">
+        <v>Volatile familiar / totem</v>
+      </c>
+      <c r="C180" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D180" s="7" t="str">
+        <v>JAC-M051, SOL-04-E03</v>
+      </c>
+      <c r="E180" s="7" t="str">
+        <v>summon</v>
+      </c>
+      <c r="F180" s="7" t="str">
+        <v>New speculative hybrid</v>
+      </c>
+      <c r="G180" s="7" t="str">
+        <v>Speculative idea; not approved</v>
+      </c>
+      <c r="H180" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#h01</v>
+      </c>
+    </row>
+    <row r="181" ht="80" customHeight="1">
+      <c r="A181" s="7" t="str">
+        <v>H02</v>
+      </c>
+      <c r="B181" s="7" t="str">
+        <v>Refracting channeled beam</v>
+      </c>
+      <c r="C181" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D181" s="7" t="str">
+        <v>JAC-M034, SOL-01-E03</v>
+      </c>
+      <c r="E181" s="7" t="str">
+        <v>beam, timing</v>
+      </c>
+      <c r="F181" s="7" t="str">
+        <v>New speculative hybrid</v>
+      </c>
+      <c r="G181" s="7" t="str">
+        <v>Speculative idea; not approved</v>
+      </c>
+      <c r="H181" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#h02</v>
+      </c>
+    </row>
+    <row r="182" ht="80" customHeight="1">
+      <c r="A182" s="7" t="str">
+        <v>H03</v>
+      </c>
+      <c r="B182" s="7" t="str">
+        <v>Chilled storm setup</v>
+      </c>
+      <c r="C182" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D182" s="7" t="str">
+        <v>JAC-M013, ECL-03-E01</v>
+      </c>
+      <c r="E182" s="7" t="str">
+        <v>control, area</v>
+      </c>
+      <c r="F182" s="7" t="str">
+        <v>New speculative hybrid</v>
+      </c>
+      <c r="G182" s="7" t="str">
+        <v>Speculative idea; not approved</v>
+      </c>
+      <c r="H182" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#h03</v>
+      </c>
+    </row>
+    <row r="183" ht="80" customHeight="1">
+      <c r="A183" s="7" t="str">
+        <v>H04</v>
+      </c>
+      <c r="B183" s="7" t="str">
+        <v>Linked healing deployables</v>
+      </c>
+      <c r="C183" s="7" t="str">
+        <v>combination</v>
+      </c>
+      <c r="D183" s="7" t="str">
+        <v>JAC-M050, GEN-06</v>
+      </c>
+      <c r="E183" s="7" t="str">
+        <v>healing, protection</v>
+      </c>
+      <c r="F183" s="7" t="str">
+        <v>New speculative hybrid</v>
+      </c>
+      <c r="G183" s="7" t="str">
+        <v>Speculative idea; not approved</v>
+      </c>
+      <c r="H183" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#h04</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="Rc369aca57c7447e1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="40" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="85" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="40" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="40" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="40" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="40" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="10" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" s="10" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C1" s="10" t="str">
+        <v>Base / Participants</v>
+      </c>
+      <c r="D1" s="10" t="str">
+        <v>Idea (draft; historical values are not balance)</v>
+      </c>
+      <c r="E1" s="10" t="str">
+        <v>Origin</v>
+      </c>
+      <c r="F1" s="10" t="str">
+        <v>Status</v>
+      </c>
+      <c r="G1" s="10" t="str">
+        <v>Provenance</v>
+      </c>
+      <c r="H1" s="10" t="str">
+        <v>Canonical detail</v>
+      </c>
+    </row>
+    <row r="2" ht="80" customHeight="1">
+      <c r="A2" s="7" t="str">
+        <v>JAC-M001</v>
+      </c>
+      <c r="B2" s="7" t="str">
+        <v>Serrated Cleave</v>
+      </c>
+      <c r="C2" s="7" t="str">
+        <v>JAC-B01</v>
+      </c>
+      <c r="D2" s="7" t="str">
+        <v>Wide Cleave applies Bleed to all enemies hit.</v>
+      </c>
+      <c r="E2" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F2" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G2" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#warrior</v>
+      </c>
+      <c r="H2" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m001</v>
+      </c>
+    </row>
+    <row r="3" ht="80" customHeight="1">
+      <c r="A3" s="7" t="str">
+        <v>JAC-M002</v>
+      </c>
+      <c r="B3" s="7" t="str">
+        <v>Blood Harvest</v>
+      </c>
+      <c r="C3" s="7" t="str">
+        <v>JAC-B01</v>
+      </c>
+      <c r="D3" s="7" t="str">
+        <v>Wide Cleave consumes Bleed stacks for self-healing.</v>
+      </c>
+      <c r="E3" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F3" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G3" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#warrior</v>
+      </c>
+      <c r="H3" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m002</v>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" s="7" t="str">
+        <v>JAC-M003</v>
+      </c>
+      <c r="B4" s="7" t="str">
+        <v>Whirlwind</v>
+      </c>
+      <c r="C4" s="7" t="str">
+        <v>JAC-B01</v>
+      </c>
+      <c r="D4" s="7" t="str">
+        <v>Wide Cleave becomes a 360-degree spin with shorter reach.</v>
+      </c>
+      <c r="E4" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F4" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G4" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#warrior</v>
+      </c>
+      <c r="H4" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m003</v>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1">
+      <c r="A5" s="7" t="str">
+        <v>JAC-M004</v>
+      </c>
+      <c r="B5" s="7" t="str">
+        <v>Executioner's Arc</v>
+      </c>
+      <c r="C5" s="7" t="str">
+        <v>JAC-B01</v>
+      </c>
+      <c r="D5" s="7" t="str">
+        <v>Narrower Cleave, stronger execute against low-HP targets.</v>
+      </c>
+      <c r="E5" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F5" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G5" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#warrior</v>
+      </c>
+      <c r="H5" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m004</v>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="7" t="str">
+        <v>JAC-M005</v>
+      </c>
+      <c r="B6" s="7" t="str">
+        <v>Unstoppable Charge</v>
+      </c>
+      <c r="C6" s="7" t="str">
+        <v>JAC-B02</v>
+      </c>
+      <c r="D6" s="7" t="str">
+        <v>Gap-closer charges through ordinary slows and knocks aside enemies.</v>
+      </c>
+      <c r="E6" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F6" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G6" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#warrior</v>
+      </c>
+      <c r="H6" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m005</v>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="7" t="str">
+        <v>JAC-M006</v>
+      </c>
+      <c r="B7" s="7" t="str">
+        <v>Rallying Cry</v>
+      </c>
+      <c r="C7" s="7" t="str">
+        <v>JAC-B03</v>
+      </c>
+      <c r="D7" s="7" t="str">
+        <v>Defensive ability becomes a short-range party damage-reduction cry.</v>
+      </c>
+      <c r="E7" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F7" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G7" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#warrior</v>
+      </c>
+      <c r="H7" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m006</v>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="7" t="str">
+        <v>JAC-M007</v>
+      </c>
+      <c r="B8" s="7" t="str">
+        <v>Shared Mend</v>
+      </c>
+      <c r="C8" s="7" t="str">
+        <v>JAC-B04</v>
+      </c>
+      <c r="D8" s="7" t="str">
+        <v>Mend heals the target and a nearby injured ally at reduced potency.</v>
+      </c>
+      <c r="E8" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F8" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G8" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#priest</v>
+      </c>
+      <c r="H8" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m007</v>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="7" t="str">
+        <v>JAC-M008</v>
+      </c>
+      <c r="B9" s="7" t="str">
+        <v>Prayer of Renewal</v>
+      </c>
+      <c r="C9" s="7" t="str">
+        <v>JAC-B04</v>
+      </c>
+      <c r="D9" s="7" t="str">
+        <v>Mend becomes healing over time instead of immediate healing.</v>
+      </c>
+      <c r="E9" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F9" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G9" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#priest</v>
+      </c>
+      <c r="H9" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m008</v>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="7" t="str">
+        <v>JAC-M009</v>
+      </c>
+      <c r="B10" s="7" t="str">
+        <v>Divine Intervention</v>
+      </c>
+      <c r="C10" s="7" t="str">
+        <v>JAC-B04</v>
+      </c>
+      <c r="D10" s="7" t="str">
+        <v>Delayed large heal after marking an ally.</v>
+      </c>
+      <c r="E10" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F10" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G10" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#priest</v>
+      </c>
+      <c r="H10" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m009</v>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="7" t="str">
+        <v>JAC-M010</v>
+      </c>
+      <c r="B11" s="7" t="str">
+        <v>Purifying Light</v>
+      </c>
+      <c r="C11" s="7" t="str">
+        <v>JAC-B05</v>
+      </c>
+      <c r="D11" s="7" t="str">
+        <v>Holy skill can remove a debuff from allies or buff from enemies.</v>
+      </c>
+      <c r="E11" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F11" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G11" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#priest</v>
+      </c>
+      <c r="H11" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m010</v>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
+      <c r="A12" s="7" t="str">
+        <v>JAC-M011</v>
+      </c>
+      <c r="B12" s="7" t="str">
+        <v>Sanctuary</v>
+      </c>
+      <c r="C12" s="7" t="str">
+        <v>JAC-B06</v>
+      </c>
+      <c r="D12" s="7" t="str">
+        <v>Protective skill becomes a stationary group damage-reduction zone.</v>
+      </c>
+      <c r="E12" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F12" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G12" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#priest</v>
+      </c>
+      <c r="H12" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m011</v>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="7" t="str">
+        <v>JAC-M012</v>
+      </c>
+      <c r="B13" s="7" t="str">
+        <v>Martyr's Bond</v>
+      </c>
+      <c r="C13" s="7" t="str">
+        <v>JAC-B07</v>
+      </c>
+      <c r="D13" s="7" t="str">
+        <v>Healing an ally damages a nearby enemy at a small personal HP cost.</v>
+      </c>
+      <c r="E13" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F13" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G13" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#priest</v>
+      </c>
+      <c r="H13" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m012</v>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
+      <c r="A14" s="7" t="str">
+        <v>JAC-M013</v>
+      </c>
+      <c r="B14" s="7" t="str">
+        <v>Blizzard</v>
+      </c>
+      <c r="C14" s="7" t="str">
+        <v>JAC-B08</v>
+      </c>
+      <c r="D14" s="7" t="str">
+        <v>Lightning Storm is replaced by Blizzard, dealing cold damage and slowing.</v>
+      </c>
+      <c r="E14" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F14" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G14" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#lightning-mage</v>
+      </c>
+      <c r="H14" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m013</v>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1">
+      <c r="A15" s="7" t="str">
+        <v>JAC-M014</v>
+      </c>
+      <c r="B15" s="7" t="str">
+        <v>Thunder Prison</v>
+      </c>
+      <c r="C15" s="7" t="str">
+        <v>JAC-B08</v>
+      </c>
+      <c r="D15" s="7" t="str">
+        <v>Lightning Storm becomes a smaller field that briefly stuns enemies trying to leave.</v>
+      </c>
+      <c r="E15" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F15" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G15" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#lightning-mage</v>
+      </c>
+      <c r="H15" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m014</v>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="7" t="str">
+        <v>JAC-M015</v>
+      </c>
+      <c r="B16" s="7" t="str">
+        <v>Storm Chaser</v>
+      </c>
+      <c r="C16" s="7" t="str">
+        <v>JAC-B08</v>
+      </c>
+      <c r="D16" s="7" t="str">
+        <v>Lightning Storm follows its target.</v>
+      </c>
+      <c r="E16" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F16" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G16" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#lightning-mage</v>
+      </c>
+      <c r="H16" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m015</v>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1">
+      <c r="A17" s="7" t="str">
+        <v>JAC-M016</v>
+      </c>
+      <c r="B17" s="7" t="str">
+        <v>Chain Reaction</v>
+      </c>
+      <c r="C17" s="7" t="str">
+        <v>JAC-B09</v>
+      </c>
+      <c r="D17" s="7" t="str">
+        <v>Chain Lightning reaches additional targets with falloff.</v>
+      </c>
+      <c r="E17" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F17" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G17" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#lightning-mage</v>
+      </c>
+      <c r="H17" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m016</v>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1">
+      <c r="A18" s="7" t="str">
+        <v>JAC-M017</v>
+      </c>
+      <c r="B18" s="7" t="str">
+        <v>Overload</v>
+      </c>
+      <c r="C18" s="7" t="str">
+        <v>JAC-B09</v>
+      </c>
+      <c r="D18" s="7" t="str">
+        <v>Chain Lightning stops chaining and instead strikes one target repeatedly.</v>
+      </c>
+      <c r="E18" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F18" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G18" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#lightning-mage</v>
+      </c>
+      <c r="H18" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m017</v>
+      </c>
+    </row>
+    <row r="19" ht="80" customHeight="1">
+      <c r="A19" s="7" t="str">
+        <v>JAC-M018</v>
+      </c>
+      <c r="B19" s="7" t="str">
+        <v>Ice Block</v>
+      </c>
+      <c r="C19" s="7" t="str">
+        <v>JAC-B10</v>
+      </c>
+      <c r="D19" s="7" t="str">
+        <v>Replace Dash with a stationary, action-locking temporary invulnerability.</v>
+      </c>
+      <c r="E19" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F19" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G19" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#lightning-mage</v>
+      </c>
+      <c r="H19" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m018</v>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1">
+      <c r="A20" s="7" t="str">
+        <v>JAC-M019</v>
+      </c>
+      <c r="B20" s="7" t="str">
+        <v>Static Discharge</v>
+      </c>
+      <c r="C20" s="7" t="str">
+        <v>JAC-B10</v>
+      </c>
+      <c r="D20" s="7" t="str">
+        <v>Mobility skill emits lightning around the landing position.</v>
+      </c>
+      <c r="E20" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F20" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G20" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#lightning-mage</v>
+      </c>
+      <c r="H20" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m019</v>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" s="7" t="str">
+        <v>JAC-M020</v>
+      </c>
+      <c r="B21" s="7" t="str">
+        <v>Endless Volley</v>
+      </c>
+      <c r="C21" s="7" t="str">
+        <v>JAC-B11</v>
+      </c>
+      <c r="D21" s="7" t="str">
+        <v>Aimed Shot charges indefinitely while held and fires an arrow every **0.8 seconds**; moving cancels the channel. Explicitly define resource cost, hold/release input, retargeting and damage balance.</v>
+      </c>
+      <c r="E21" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F21" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G21" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#ranger</v>
+      </c>
+      <c r="H21" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m020</v>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" s="7" t="str">
+        <v>JAC-M021</v>
+      </c>
+      <c r="B22" s="7" t="str">
+        <v>Sniper's Patience</v>
+      </c>
+      <c r="C22" s="7" t="str">
+        <v>JAC-B11</v>
+      </c>
+      <c r="D22" s="7" t="str">
+        <v>Longer Aimed Shot charge for range and power; movement interrupts.</v>
+      </c>
+      <c r="E22" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F22" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G22" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#ranger</v>
+      </c>
+      <c r="H22" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m021</v>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1">
+      <c r="A23" s="7" t="str">
+        <v>JAC-M022</v>
+      </c>
+      <c r="B23" s="7" t="str">
+        <v>Splinter Shot</v>
+      </c>
+      <c r="C23" s="7" t="str">
+        <v>JAC-B11</v>
+      </c>
+      <c r="D23" s="7" t="str">
+        <v>Aimed Shot fires three arrows in a spread.</v>
+      </c>
+      <c r="E23" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F23" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G23" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#ranger</v>
+      </c>
+      <c r="H23" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m022</v>
+      </c>
+    </row>
+    <row r="24" ht="80" customHeight="1">
+      <c r="A24" s="7" t="str">
+        <v>JAC-M023</v>
+      </c>
+      <c r="B24" s="7" t="str">
+        <v>Pinning Arrow</v>
+      </c>
+      <c r="C24" s="7" t="str">
+        <v>JAC-B11</v>
+      </c>
+      <c r="D24" s="7" t="str">
+        <v>Fully charged Aimed Shot briefly roots.</v>
+      </c>
+      <c r="E24" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F24" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G24" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#ranger</v>
+      </c>
+      <c r="H24" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m023</v>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1">
+      <c r="A25" s="7" t="str">
+        <v>JAC-M024</v>
+      </c>
+      <c r="B25" s="7" t="str">
+        <v>Ricochet Arrow</v>
+      </c>
+      <c r="C25" s="7" t="str">
+        <v>JAC-B11</v>
+      </c>
+      <c r="D25" s="7" t="str">
+        <v>Aimed Shot seeks a second target after impact.</v>
+      </c>
+      <c r="E25" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F25" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G25" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#ranger</v>
+      </c>
+      <c r="H25" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m024</v>
+      </c>
+    </row>
+    <row r="26" ht="80" customHeight="1">
+      <c r="A26" s="7" t="str">
+        <v>JAC-M025</v>
+      </c>
+      <c r="B26" s="7" t="str">
+        <v>Explosive Tip</v>
+      </c>
+      <c r="C26" s="7" t="str">
+        <v>JAC-B11</v>
+      </c>
+      <c r="D26" s="7" t="str">
+        <v>Aimed Shot explodes in an area.</v>
+      </c>
+      <c r="E26" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F26" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G26" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#ranger</v>
+      </c>
+      <c r="H26" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m025</v>
+      </c>
+    </row>
+    <row r="27" ht="80" customHeight="1">
+      <c r="A27" s="7" t="str">
+        <v>JAC-M026</v>
+      </c>
+      <c r="B27" s="7" t="str">
+        <v>Rolling Escape</v>
+      </c>
+      <c r="C27" s="7" t="str">
+        <v>JAC-B10</v>
+      </c>
+      <c r="D27" s="7" t="str">
+        <v>Dash becomes a shorter dodge roll with brief invulnerability.</v>
+      </c>
+      <c r="E27" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F27" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G27" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#ranger</v>
+      </c>
+      <c r="H27" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m026</v>
+      </c>
+    </row>
+    <row r="28" ht="80" customHeight="1">
+      <c r="A28" s="7" t="str">
+        <v>JAC-M027</v>
+      </c>
+      <c r="B28" s="7" t="str">
+        <v>Lobbed Fireball</v>
+      </c>
+      <c r="C28" s="7" t="str">
+        <v>JAC-B12</v>
+      </c>
+      <c r="D28" s="7" t="str">
+        <v>Fireball becomes an **arcing ground-targeted projectile** that can pass **over pillars/cover**, then explodes at the target location. It should not arbitrarily ignore all obstacles or arena boundaries.</v>
+      </c>
+      <c r="E28" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F28" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G28" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#fire-mage</v>
+      </c>
+      <c r="H28" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m027</v>
+      </c>
+    </row>
+    <row r="29" ht="80" customHeight="1">
+      <c r="A29" s="7" t="str">
+        <v>JAC-M028</v>
+      </c>
+      <c r="B29" s="7" t="str">
+        <v>Living Flame</v>
+      </c>
+      <c r="C29" s="7" t="str">
+        <v>JAC-B12</v>
+      </c>
+      <c r="D29" s="7" t="str">
+        <v>Fireball leaves a burning patch.</v>
+      </c>
+      <c r="E29" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F29" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G29" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#fire-mage</v>
+      </c>
+      <c r="H29" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m028</v>
+      </c>
+    </row>
+    <row r="30" ht="80" customHeight="1">
+      <c r="A30" s="7" t="str">
+        <v>JAC-M029</v>
+      </c>
+      <c r="B30" s="7" t="str">
+        <v>Cluster Fireball</v>
+      </c>
+      <c r="C30" s="7" t="str">
+        <v>JAC-B12</v>
+      </c>
+      <c r="D30" s="7" t="str">
+        <v>Fireball breaks into three smaller impact explosions.</v>
+      </c>
+      <c r="E30" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F30" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G30" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#fire-mage</v>
+      </c>
+      <c r="H30" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m029</v>
+      </c>
+    </row>
+    <row r="31" ht="80" customHeight="1">
+      <c r="A31" s="7" t="str">
+        <v>JAC-M030</v>
+      </c>
+      <c r="B31" s="7" t="str">
+        <v>Flamethrower</v>
+      </c>
+      <c r="C31" s="7" t="str">
+        <v>JAC-B12</v>
+      </c>
+      <c r="D31" s="7" t="str">
+        <v>Replace Fireball with a channeled frontal cone.</v>
+      </c>
+      <c r="E31" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F31" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G31" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#fire-mage</v>
+      </c>
+      <c r="H31" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m030</v>
+      </c>
+    </row>
+    <row r="32" ht="80" customHeight="1">
+      <c r="A32" s="7" t="str">
+        <v>JAC-M031</v>
+      </c>
+      <c r="B32" s="7" t="str">
+        <v>Meteor</v>
+      </c>
+      <c r="C32" s="7" t="str">
+        <v>JAC-B12</v>
+      </c>
+      <c r="D32" s="7" t="str">
+        <v>Replace Fireball with a delayed large AoE impact.</v>
+      </c>
+      <c r="E32" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F32" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G32" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#fire-mage</v>
+      </c>
+      <c r="H32" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m031</v>
+      </c>
+    </row>
+    <row r="33" ht="80" customHeight="1">
+      <c r="A33" s="7" t="str">
+        <v>JAC-M032</v>
+      </c>
+      <c r="B33" s="7" t="str">
+        <v>Phoenix Dash</v>
+      </c>
+      <c r="C33" s="7" t="str">
+        <v>JAC-B10</v>
+      </c>
+      <c r="D33" s="7" t="str">
+        <v>Dash leaves a burning trail.</v>
+      </c>
+      <c r="E33" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F33" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G33" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#fire-mage</v>
+      </c>
+      <c r="H33" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m032</v>
+      </c>
+    </row>
+    <row r="34" ht="80" customHeight="1">
+      <c r="A34" s="7" t="str">
+        <v>JAC-M033</v>
+      </c>
+      <c r="B34" s="7" t="str">
+        <v>Cauterize</v>
+      </c>
+      <c r="C34" s="7" t="str">
+        <v>JAC-B13</v>
+      </c>
+      <c r="D34" s="7" t="str">
+        <v>Fire damage-over-time can instead target allies as healing-over-time (requires careful target-mode rules).</v>
+      </c>
+      <c r="E34" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F34" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G34" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#fire-mage</v>
+      </c>
+      <c r="H34" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m033</v>
+      </c>
+    </row>
+    <row r="35" ht="80" customHeight="1">
+      <c r="A35" s="7" t="str">
+        <v>JAC-M034</v>
+      </c>
+      <c r="B35" s="7" t="str">
+        <v>Refracting LAZOR</v>
+      </c>
+      <c r="C35" s="7" t="str">
+        <v>JAC-B14</v>
+      </c>
+      <c r="D35" s="7" t="str">
+        <v>LAZOR splits/refracts into weaker beams after striking enemies or cover; cap beam count and ensure pillars remain meaningful.</v>
+      </c>
+      <c r="E35" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F35" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G35" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#defender</v>
+      </c>
+      <c r="H35" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m034</v>
+      </c>
+    </row>
+    <row r="36" ht="80" customHeight="1">
+      <c r="A36" s="7" t="str">
+        <v>JAC-M035</v>
+      </c>
+      <c r="B36" s="7" t="str">
+        <v>Sweeping LAZOR</v>
+      </c>
+      <c r="C36" s="7" t="str">
+        <v>JAC-B14</v>
+      </c>
+      <c r="D36" s="7" t="str">
+        <v>LAZOR becomes a steerable channeled beam.</v>
+      </c>
+      <c r="E36" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F36" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G36" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#defender</v>
+      </c>
+      <c r="H36" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m035</v>
+      </c>
+    </row>
+    <row r="37" ht="80" customHeight="1">
+      <c r="A37" s="7" t="str">
+        <v>JAC-M036</v>
+      </c>
+      <c r="B37" s="7" t="str">
+        <v>Piercing LAZOR</v>
+      </c>
+      <c r="C37" s="7" t="str">
+        <v>JAC-B14</v>
+      </c>
+      <c r="D37" s="7" t="str">
+        <v>Narrower LAZOR passes through enemies.</v>
+      </c>
+      <c r="E37" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F37" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G37" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#defender</v>
+      </c>
+      <c r="H37" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m036</v>
+      </c>
+    </row>
+    <row r="38" ht="80" customHeight="1">
+      <c r="A38" s="7" t="str">
+        <v>JAC-M037</v>
+      </c>
+      <c r="B38" s="7" t="str">
+        <v>Guardian Bulwark</v>
+      </c>
+      <c r="C38" s="7" t="str">
+        <v>JAC-B15</v>
+      </c>
+      <c r="D38" s="7" t="str">
+        <v>Bulwark also protects nearby allies.</v>
+      </c>
+      <c r="E38" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F38" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G38" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#defender</v>
+      </c>
+      <c r="H38" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m037</v>
+      </c>
+    </row>
+    <row r="39" ht="80" customHeight="1">
+      <c r="A39" s="7" t="str">
+        <v>JAC-M038</v>
+      </c>
+      <c r="B39" s="7" t="str">
+        <v>Reflective Bulwark</v>
+      </c>
+      <c r="C39" s="7" t="str">
+        <v>JAC-B15</v>
+      </c>
+      <c r="D39" s="7" t="str">
+        <v>Bulwark reflects some incoming damage.</v>
+      </c>
+      <c r="E39" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F39" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G39" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#defender</v>
+      </c>
+      <c r="H39" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m038</v>
+      </c>
+    </row>
+    <row r="40" ht="80" customHeight="1">
+      <c r="A40" s="7" t="str">
+        <v>JAC-M039</v>
+      </c>
+      <c r="B40" s="7" t="str">
+        <v>Fortress Mode</v>
+      </c>
+      <c r="C40" s="7" t="str">
+        <v>JAC-B15</v>
+      </c>
+      <c r="D40" s="7" t="str">
+        <v>Bulwark roots the Defender in exchange for stronger mitigation/knockback immunity.</v>
+      </c>
+      <c r="E40" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F40" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G40" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#defender</v>
+      </c>
+      <c r="H40" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m039</v>
+      </c>
+    </row>
+    <row r="41" ht="80" customHeight="1">
+      <c r="A41" s="7" t="str">
+        <v>JAC-M040</v>
+      </c>
+      <c r="B41" s="7" t="str">
+        <v>Sacrificial Guard</v>
+      </c>
+      <c r="C41" s="7" t="str">
+        <v>JAC-B15</v>
+      </c>
+      <c r="D41" s="7" t="str">
+        <v>Bulwark redirects part of a selected ally's incoming damage to the Defender.</v>
+      </c>
+      <c r="E41" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F41" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G41" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#defender</v>
+      </c>
+      <c r="H41" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m040</v>
+      </c>
+    </row>
+    <row r="42" ht="80" customHeight="1">
+      <c r="A42" s="7" t="str">
+        <v>JAC-M041</v>
+      </c>
+      <c r="B42" s="7" t="str">
+        <v>Contagious Poison</v>
+      </c>
+      <c r="C42" s="7" t="str">
+        <v>JAC-B16</v>
+      </c>
+      <c r="D42" s="7" t="str">
+        <v>**Poison Enchant can target allies**, enchanting their attacks.</v>
+      </c>
+      <c r="E42" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F42" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G42" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#rogue</v>
+      </c>
+      <c r="H42" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m041</v>
+      </c>
+    </row>
+    <row r="43" ht="80" customHeight="1">
+      <c r="A43" s="7" t="str">
+        <v>JAC-M042</v>
+      </c>
+      <c r="B43" s="7" t="str">
+        <v>Fleet Venom</v>
+      </c>
+      <c r="C43" s="7" t="str">
+        <v>JAC-B16</v>
+      </c>
+      <c r="D43" s="7" t="str">
+        <v>Poison Enchant also **increases the enchanted player's movement speed**.</v>
+      </c>
+      <c r="E43" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F43" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G43" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#rogue</v>
+      </c>
+      <c r="H43" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m042</v>
+      </c>
+    </row>
+    <row r="44" ht="80" customHeight="1">
+      <c r="A44" s="7" t="str">
+        <v>JAC-M043</v>
+      </c>
+      <c r="B44" s="7" t="str">
+        <v>Paralytic Venom</v>
+      </c>
+      <c r="C44" s="7" t="str">
+        <v>JAC-B17</v>
+      </c>
+      <c r="D44" s="7" t="str">
+        <v>Replace poison damage with a stacking slow.</v>
+      </c>
+      <c r="E44" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F44" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G44" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#rogue</v>
+      </c>
+      <c r="H44" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m043</v>
+      </c>
+    </row>
+    <row r="45" ht="80" customHeight="1">
+      <c r="A45" s="7" t="str">
+        <v>JAC-M044</v>
+      </c>
+      <c r="B45" s="7" t="str">
+        <v>Explosive Venom</v>
+      </c>
+      <c r="C45" s="7" t="str">
+        <v>JAC-B18</v>
+      </c>
+      <c r="D45" s="7" t="str">
+        <v>Poisoned enemies explode on death, spreading poison.</v>
+      </c>
+      <c r="E45" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F45" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G45" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#rogue</v>
+      </c>
+      <c r="H45" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m044</v>
+      </c>
+    </row>
+    <row r="46" ht="80" customHeight="1">
+      <c r="A46" s="7" t="str">
+        <v>JAC-M045</v>
+      </c>
+      <c r="B46" s="7" t="str">
+        <v>Shadowstep</v>
+      </c>
+      <c r="C46" s="7" t="str">
+        <v>JAC-B10</v>
+      </c>
+      <c r="D46" s="7" t="str">
+        <v>Dash becomes a short teleport that passes through pillars.</v>
+      </c>
+      <c r="E46" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F46" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G46" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#rogue</v>
+      </c>
+      <c r="H46" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m045</v>
+      </c>
+    </row>
+    <row r="47" ht="80" customHeight="1">
+      <c r="A47" s="7" t="str">
+        <v>JAC-M046</v>
+      </c>
+      <c r="B47" s="7" t="str">
+        <v>Smoke Bomb</v>
+      </c>
+      <c r="C47" s="7" t="str">
+        <v>JAC-B10</v>
+      </c>
+      <c r="D47" s="7" t="str">
+        <v>Replace Dash with a smoke field that conceals allies inside.</v>
+      </c>
+      <c r="E47" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F47" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G47" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#rogue</v>
+      </c>
+      <c r="H47" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m046</v>
+      </c>
+    </row>
+    <row r="48" ht="80" customHeight="1">
+      <c r="A48" s="7" t="str">
+        <v>JAC-M047</v>
+      </c>
+      <c r="B48" s="7" t="str">
+        <v>Ambush</v>
+      </c>
+      <c r="C48" s="7" t="str">
+        <v>JAC-B19</v>
+      </c>
+      <c r="D48" s="7" t="str">
+        <v>Backstab is stronger from stealth and weaker outside stealth.</v>
+      </c>
+      <c r="E48" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F48" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G48" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#rogue</v>
+      </c>
+      <c r="H48" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m047</v>
+      </c>
+    </row>
+    <row r="49" ht="80" customHeight="1">
+      <c r="A49" s="7" t="str">
+        <v>JAC-M048</v>
+      </c>
+      <c r="B49" s="7" t="str">
+        <v>Totemic Legion</v>
+      </c>
+      <c r="C49" s="7" t="str">
+        <v>JAC-B20</v>
+      </c>
+      <c r="D49" s="7" t="str">
+        <v>Permit **multiple simultaneous Healing Totems** (suggest up to three) with reduced healing per totem; avoid uncapped stacking.</v>
+      </c>
+      <c r="E49" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F49" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G49" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#shaman</v>
+      </c>
+      <c r="H49" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m048</v>
+      </c>
+    </row>
+    <row r="50" ht="80" customHeight="1">
+      <c r="A50" s="7" t="str">
+        <v>JAC-M049</v>
+      </c>
+      <c r="B50" s="7" t="str">
+        <v>Ancestral Totem</v>
+      </c>
+      <c r="C50" s="7" t="str">
+        <v>JAC-B20</v>
+      </c>
+      <c r="D50" s="7" t="str">
+        <v>Healing Totem becomes a larger persistent healing field with a longer cooldown.</v>
+      </c>
+      <c r="E50" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F50" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G50" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#shaman</v>
+      </c>
+      <c r="H50" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m049</v>
+      </c>
+    </row>
+    <row r="51" ht="80" customHeight="1">
+      <c r="A51" s="7" t="str">
+        <v>JAC-M050</v>
+      </c>
+      <c r="B51" s="7" t="str">
+        <v>Spirit Link</v>
+      </c>
+      <c r="C51" s="7" t="str">
+        <v>JAC-B20</v>
+      </c>
+      <c r="D51" s="7" t="str">
+        <v>Healing Totem redistributes some damage among allies in range.</v>
+      </c>
+      <c r="E51" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F51" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G51" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#shaman</v>
+      </c>
+      <c r="H51" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m050</v>
+      </c>
+    </row>
+    <row r="52" ht="80" customHeight="1">
+      <c r="A52" s="7" t="str">
+        <v>JAC-M051</v>
+      </c>
+      <c r="B52" s="7" t="str">
+        <v>Volatile Totem</v>
+      </c>
+      <c r="C52" s="7" t="str">
+        <v>JAC-B21</v>
+      </c>
+      <c r="D52" s="7" t="str">
+        <v>**Fire Totem explodes when it dies** or expires.</v>
+      </c>
+      <c r="E52" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F52" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G52" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#shaman</v>
+      </c>
+      <c r="H52" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m051</v>
+      </c>
+    </row>
+    <row r="53" ht="80" customHeight="1">
+      <c r="A53" s="7" t="str">
+        <v>JAC-M052</v>
+      </c>
+      <c r="B53" s="7" t="str">
+        <v>Flamecaller</v>
+      </c>
+      <c r="C53" s="7" t="str">
+        <v>JAC-B21</v>
+      </c>
+      <c r="D53" s="7" t="str">
+        <v>Fire Totem attacks faster but is more fragile.</v>
+      </c>
+      <c r="E53" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F53" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G53" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#shaman</v>
+      </c>
+      <c r="H53" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m052</v>
+      </c>
+    </row>
+    <row r="54" ht="80" customHeight="1">
+      <c r="A54" s="7" t="str">
+        <v>JAC-M053</v>
+      </c>
+      <c r="B54" s="7" t="str">
+        <v>Walking Totem</v>
+      </c>
+      <c r="C54" s="7" t="str">
+        <v>JAC-B21</v>
+      </c>
+      <c r="D54" s="7" t="str">
+        <v>Fire Totem follows its caster.</v>
+      </c>
+      <c r="E54" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F54" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G54" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#shaman</v>
+      </c>
+      <c r="H54" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m053</v>
+      </c>
+    </row>
+    <row r="55" ht="80" customHeight="1">
+      <c r="A55" s="7" t="str">
+        <v>JAC-M054</v>
+      </c>
+      <c r="B55" s="7" t="str">
+        <v>Earthbind</v>
+      </c>
+      <c r="C55" s="7" t="str">
+        <v>JAC-B22</v>
+      </c>
+      <c r="D55" s="7" t="str">
+        <v>Earth Shock becomes an AoE slow rather than single-target burst.</v>
+      </c>
+      <c r="E55" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F55" s="7" t="str">
+        <v>Draft idea; not approved</v>
+      </c>
+      <c r="G55" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#shaman</v>
+      </c>
+      <c r="H55" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-m054</v>
+      </c>
+    </row>
+    <row r="56" ht="80" customHeight="1">
+      <c r="A56" s="7" t="str">
+        <v>JAC-I001</v>
+      </c>
+      <c r="B56" s="7" t="str">
+        <v>Hit-absorbing skeletons</v>
+      </c>
+      <c r="C56" s="7" t="str">
+        <v>JAC-B23</v>
+      </c>
+      <c r="D56" s="7" t="str">
+        <v>Skeletons absorb hits; tankier-skeleton build idea.</v>
+      </c>
+      <c r="E56" s="7" t="str">
+        <v>Axel design interview</v>
+      </c>
+      <c r="F56" s="7" t="str">
+        <v>Draft interview idea; not approved</v>
+      </c>
+      <c r="G56" s="7" t="str">
+        <v>../DESIGN_INTERVIEW_AXEL.md#classes--builds</v>
+      </c>
+      <c r="H56" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-i001</v>
+      </c>
+    </row>
+    <row r="57" ht="80" customHeight="1">
+      <c r="A57" s="7" t="str">
+        <v>JAC-I002</v>
+      </c>
+      <c r="B57" s="7" t="str">
+        <v>Melee skeletons</v>
+      </c>
+      <c r="C57" s="7" t="str">
+        <v>JAC-B23</v>
+      </c>
+      <c r="D57" s="7" t="str">
+        <v>Build idea focused on stronger melee skeletons.</v>
+      </c>
+      <c r="E57" s="7" t="str">
+        <v>Axel design interview</v>
+      </c>
+      <c r="F57" s="7" t="str">
+        <v>Draft interview idea; not approved</v>
+      </c>
+      <c r="G57" s="7" t="str">
+        <v>../DESIGN_INTERVIEW_AXEL.md#classes--builds</v>
+      </c>
+      <c r="H57" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-i002</v>
+      </c>
+    </row>
+    <row r="58" ht="80" customHeight="1">
+      <c r="A58" s="7" t="str">
+        <v>JAC-I003</v>
+      </c>
+      <c r="B58" s="7" t="str">
+        <v>Debuffing mage skeletons</v>
+      </c>
+      <c r="C58" s="7" t="str">
+        <v>JAC-B23</v>
+      </c>
+      <c r="D58" s="7" t="str">
+        <v>Build idea focused on debuffing mage skeletons.</v>
+      </c>
+      <c r="E58" s="7" t="str">
+        <v>Axel design interview</v>
+      </c>
+      <c r="F58" s="7" t="str">
+        <v>Draft interview idea; not approved</v>
+      </c>
+      <c r="G58" s="7" t="str">
+        <v>../DESIGN_INTERVIEW_AXEL.md#classes--builds</v>
+      </c>
+      <c r="H58" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-i003</v>
+      </c>
+    </row>
+    <row r="59" ht="80" customHeight="1">
+      <c r="A59" s="7" t="str">
+        <v>JAC-I004</v>
+      </c>
+      <c r="B59" s="7" t="str">
+        <v>Healing skeletons</v>
+      </c>
+      <c r="C59" s="7" t="str">
+        <v>JAC-B23</v>
+      </c>
+      <c r="D59" s="7" t="str">
+        <v>Build idea focused on healing skeletons.</v>
+      </c>
+      <c r="E59" s="7" t="str">
+        <v>Axel design interview</v>
+      </c>
+      <c r="F59" s="7" t="str">
+        <v>Draft interview idea; not approved</v>
+      </c>
+      <c r="G59" s="7" t="str">
+        <v>../DESIGN_INTERVIEW_AXEL.md#classes--builds</v>
+      </c>
+      <c r="H59" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-i004</v>
+      </c>
+    </row>
+    <row r="60" ht="80" customHeight="1">
+      <c r="A60" s="7" t="str">
+        <v>JAC-I005</v>
+      </c>
+      <c r="B60" s="7" t="str">
+        <v>Hold Frostbite stacks</v>
+      </c>
+      <c r="C60" s="7" t="str">
+        <v>JAC-B24</v>
+      </c>
+      <c r="D60" s="7" t="str">
+        <v>Snowball gains damage per Frostbite stack; deliberately hold stacks instead of detonating. Historical example uses +5% and nine stacks; not JAC balance.</v>
+      </c>
+      <c r="E60" s="7" t="str">
+        <v>Axel design interview</v>
+      </c>
+      <c r="F60" s="7" t="str">
+        <v>Draft interview idea; not approved</v>
+      </c>
+      <c r="G60" s="7" t="str">
+        <v>../DESIGN_INTERVIEW_AXEL.md#classes--builds</v>
+      </c>
+      <c r="H60" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-i005</v>
+      </c>
+    </row>
+    <row r="61" ht="80" customHeight="1">
+      <c r="A61" s="7" t="str">
+        <v>JAC-I006</v>
+      </c>
+      <c r="B61" s="7" t="str">
+        <v>Trigger Frostbite explosions</v>
+      </c>
+      <c r="C61" s="7" t="str">
+        <v>JAC-B24</v>
+      </c>
+      <c r="D61" s="7" t="str">
+        <v>Snowball applies extra Frostbite stacks to trigger explosions frequently. Historical example uses two stacks and a ten-stack explosion; not JAC balance.</v>
+      </c>
+      <c r="E61" s="7" t="str">
+        <v>Axel design interview</v>
+      </c>
+      <c r="F61" s="7" t="str">
+        <v>Draft interview idea; not approved</v>
+      </c>
+      <c r="G61" s="7" t="str">
+        <v>../DESIGN_INTERVIEW_AXEL.md#classes--builds</v>
+      </c>
+      <c r="H61" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-i006</v>
+      </c>
+    </row>
+    <row r="62" ht="80" customHeight="1">
+      <c r="A62" s="7" t="str">
+        <v>JAC-I007</v>
+      </c>
+      <c r="B62" s="7" t="str">
+        <v>Tactical crystal payoff</v>
+      </c>
+      <c r="C62" s="7" t="str">
+        <v>JAC-B25</v>
+      </c>
+      <c r="D62" s="7" t="str">
+        <v>Attack a crystal instead of the boss for a temporary damage buff or heal. Encounter interaction idea, not an acquisition decision; historical example is +50% for ten seconds.</v>
+      </c>
+      <c r="E62" s="7" t="str">
+        <v>Axel design interview</v>
+      </c>
+      <c r="F62" s="7" t="str">
+        <v>Draft interview idea; not approved</v>
+      </c>
+      <c r="G62" s="7" t="str">
+        <v>../DESIGN_INTERVIEW_AXEL.md</v>
+      </c>
+      <c r="H62" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jac-i007</v>
+      </c>
+    </row>
+    <row r="63" ht="80" customHeight="1">
+      <c r="A63" s="7" t="str">
+        <v>JC01</v>
+      </c>
+      <c r="B63" s="7" t="str">
+        <v>Lobbed Fireball + Living Flame</v>
+      </c>
+      <c r="C63" s="7" t="str">
+        <v>JAC-M027, JAC-M028</v>
+      </c>
+      <c r="D63" s="7" t="str">
+        <v>Arc over cover and leave a burning patch.</v>
+      </c>
+      <c r="E63" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F63" s="7" t="str">
+        <v>Speculative idea; not approved</v>
+      </c>
+      <c r="G63" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#combining-mutations-suggested-rules</v>
+      </c>
+      <c r="H63" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jc01</v>
+      </c>
+    </row>
+    <row r="64" ht="80" customHeight="1">
+      <c r="A64" s="7" t="str">
+        <v>JC02</v>
+      </c>
+      <c r="B64" s="7" t="str">
+        <v>Contagious Poison + Fleet Venom</v>
+      </c>
+      <c r="C64" s="7" t="str">
+        <v>JAC-M041, JAC-M042</v>
+      </c>
+      <c r="D64" s="7" t="str">
+        <v>Ally-targetable poison enchant with movement utility.</v>
+      </c>
+      <c r="E64" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F64" s="7" t="str">
+        <v>Speculative idea; not approved</v>
+      </c>
+      <c r="G64" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#combining-mutations-suggested-rules</v>
+      </c>
+      <c r="H64" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jc02</v>
+      </c>
+    </row>
+    <row r="65" ht="80" customHeight="1">
+      <c r="A65" s="7" t="str">
+        <v>JC03</v>
+      </c>
+      <c r="B65" s="7" t="str">
+        <v>Totemic Legion + Ancestral Totem</v>
+      </c>
+      <c r="C65" s="7" t="str">
+        <v>JAC-M048, JAC-M049</v>
+      </c>
+      <c r="D65" s="7" t="str">
+        <v>Multiple persistent healing fields; compatibility and stacking unresolved.</v>
+      </c>
+      <c r="E65" s="7" t="str">
+        <v>Earlier JAC brainstorm</v>
+      </c>
+      <c r="F65" s="7" t="str">
+        <v>Speculative idea; not approved</v>
+      </c>
+      <c r="G65" s="7" t="str">
+        <v>../SKILL_MUTATION_CRAFTING_PROPOSALS.md#combining-mutations-suggested-rules</v>
+      </c>
+      <c r="H65" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#jc03</v>
+      </c>
+    </row>
+    <row r="66" ht="80" customHeight="1">
+      <c r="A66" s="7" t="str">
+        <v>H01</v>
+      </c>
+      <c r="B66" s="7" t="str">
+        <v>Volatile familiar / totem</v>
+      </c>
+      <c r="C66" s="7" t="str">
+        <v>JAC-M051, SOL-04-E03</v>
+      </c>
+      <c r="D66" s="7" t="str">
+        <v>Explore an active summon sacrifice or expiry explosion; do not assume familiar and totem lifecycles are interchangeable.</v>
+      </c>
+      <c r="E66" s="7" t="str">
+        <v>New speculative hybrid</v>
+      </c>
+      <c r="F66" s="7" t="str">
+        <v>Speculative idea; not approved</v>
+      </c>
+      <c r="G66" s="7" t="str">
+        <v>Editorial synthesis in this library; no earlier attribution</v>
+      </c>
+      <c r="H66" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#h01</v>
+      </c>
+    </row>
+    <row r="67" ht="80" customHeight="1">
+      <c r="A67" s="7" t="str">
+        <v>H02</v>
+      </c>
+      <c r="B67" s="7" t="str">
+        <v>Refracting channeled beam</v>
+      </c>
+      <c r="C67" s="7" t="str">
+        <v>JAC-M034, SOL-01-E03</v>
+      </c>
+      <c r="D67" s="7" t="str">
+        <v>Explore aimed channel plus refraction; cover behavior, input and overlap remain questions.</v>
+      </c>
+      <c r="E67" s="7" t="str">
+        <v>New speculative hybrid</v>
+      </c>
+      <c r="F67" s="7" t="str">
+        <v>Speculative idea; not approved</v>
+      </c>
+      <c r="G67" s="7" t="str">
+        <v>Editorial synthesis in this library; no earlier attribution</v>
+      </c>
+      <c r="H67" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#h02</v>
+      </c>
+    </row>
+    <row r="68" ht="80" customHeight="1">
+      <c r="A68" s="7" t="str">
+        <v>H03</v>
+      </c>
+      <c r="B68" s="7" t="str">
+        <v>Chilled storm setup</v>
+      </c>
+      <c r="C68" s="7" t="str">
+        <v>JAC-M013, ECL-03-E01</v>
+      </c>
+      <c r="D68" s="7" t="str">
+        <v>Explore a slowing field preparing a focused hit; no shared status contract is approved.</v>
+      </c>
+      <c r="E68" s="7" t="str">
+        <v>New speculative hybrid</v>
+      </c>
+      <c r="F68" s="7" t="str">
+        <v>Speculative idea; not approved</v>
+      </c>
+      <c r="G68" s="7" t="str">
+        <v>Editorial synthesis in this library; no earlier attribution</v>
+      </c>
+      <c r="H68" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#h03</v>
+      </c>
+    </row>
+    <row r="69" ht="80" customHeight="1">
+      <c r="A69" s="7" t="str">
+        <v>H04</v>
+      </c>
+      <c r="B69" s="7" t="str">
+        <v>Linked healing deployables</v>
+      </c>
+      <c r="C69" s="7" t="str">
+        <v>JAC-M050, GEN-06</v>
+      </c>
+      <c r="D69" s="7" t="str">
+        <v>Explore deployable healing with a linked-protection motif; damage transfer and healing semantics unresolved.</v>
+      </c>
+      <c r="E69" s="7" t="str">
+        <v>New speculative hybrid</v>
+      </c>
+      <c r="F69" s="7" t="str">
+        <v>Speculative idea; not approved</v>
+      </c>
+      <c r="G69" s="7" t="str">
+        <v>Editorial synthesis in this library; no earlier attribution</v>
+      </c>
+      <c r="H69" s="7" t="str">
+        <v>https://github.com/JonatanNorrby/jacworks/blob/docs/unified-ability-idea-library/DOCS/ABILITY_IDEAS/JAC_Works_Ability_Idea_Library.md#h04</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="R66cd5213ab3448cc"/>
+  </tableParts>
+</worksheet>
 </file>